--- a/AAII_Financials/Quarterly/PUK_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PUK_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,7 +17,7 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 

--- a/AAII_Financials/Quarterly/PUK_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PUK_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="92">
   <si>
     <t>PUK</t>
   </si>
@@ -656,263 +656,275 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:U102"/>
+  <dimension ref="A5:V102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="21" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="22" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45107</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44742</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44561</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44377</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44196</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44012</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43830</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>43646</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>43465</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>43281</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>43100</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>42916</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>42735</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>42551</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>42369</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>42185</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>42004</v>
       </c>
     </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>5324000</v>
+      </c>
+      <c r="E8" s="3">
         <v>5336000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>4754000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>2243000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>14808000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>11692000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>42311000</v>
       </c>
-      <c r="J8" s="3" t="s">
+      <c r="K8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>41197000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>52539000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>35845000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>16019000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>43466000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>42924000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>36301000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>45947800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>20902900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>33287100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>38844000</v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E9" s="3">
+      <c r="E9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" s="3">
         <v>1205000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1120000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1063000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1026000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>647000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>1433000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2068000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2109000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>6103000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>3186000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1792000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1920000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1987000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>2197800</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>2210800</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>2080500</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>4498200</v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E10" s="3">
+      <c r="E10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" s="3">
         <v>3549000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>1123000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>13745000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>10666000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>41664000</v>
       </c>
-      <c r="J10" s="3" t="s">
+      <c r="K10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>39129000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>50430000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>29742000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>12833000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>41674000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>41004000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>34314000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>43750000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>18692100</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>31206600</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>34345800</v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -934,8 +946,9 @@
       <c r="S11" s="3"/>
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V11" s="3"/>
+    </row>
+    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -993,8 +1006,11 @@
       <c r="U12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1052,99 +1068,105 @@
       <c r="U13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>0</v>
+        <v>22000</v>
       </c>
       <c r="E14" s="3">
+        <v>0</v>
+      </c>
+      <c r="F14" s="3">
         <v>7000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>-62000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-21000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>56000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>30000</v>
       </c>
-      <c r="J14" s="3">
-        <v>0</v>
-      </c>
       <c r="K14" s="3">
+        <v>0</v>
+      </c>
+      <c r="L14" s="3">
         <v>159000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-17000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>182000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>570000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>-162000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>-66000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>238000</v>
       </c>
-      <c r="R14" s="3" t="s">
+      <c r="S14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S14" s="3">
-        <v>0</v>
-      </c>
       <c r="T14" s="3">
         <v>0</v>
       </c>
       <c r="U14" s="3">
+        <v>0</v>
+      </c>
+      <c r="V14" s="3">
         <v>2600</v>
       </c>
     </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E15" s="3">
+      <c r="E15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F15" s="3">
         <v>74000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>71000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>61000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>85000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>77000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>109000</v>
       </c>
-      <c r="K15" s="3" t="s">
+      <c r="L15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>107000</v>
-      </c>
-      <c r="M15" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="N15" s="3" t="s">
         <v>8</v>
@@ -1155,11 +1177,11 @@
       <c r="P15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q15" s="3">
-        <v>0</v>
-      </c>
-      <c r="R15" s="3" t="s">
+      <c r="Q15" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="R15" s="3">
+        <v>0</v>
       </c>
       <c r="S15" s="3" t="s">
         <v>8</v>
@@ -1170,8 +1192,11 @@
       <c r="U15" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="V15" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1190,126 +1215,133 @@
       <c r="S16" s="3"/>
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
-    </row>
-    <row r="17" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V16" s="3"/>
+    </row>
+    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>4384000</v>
+      </c>
+      <c r="E17" s="3">
         <v>4088000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>4019000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>3536000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>13404000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>10444000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>40297000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>-6757000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>40471000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>51224000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>32167000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>14313000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>41957000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>41014000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>34595000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>44982000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>19189000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>30714100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>37257300</v>
       </c>
     </row>
-    <row r="18" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>940000</v>
+      </c>
+      <c r="E18" s="3">
         <v>1248000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>735000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-1293000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>1404000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>1248000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>2014000</v>
       </c>
-      <c r="J18" s="3" t="s">
+      <c r="K18" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>726000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>1315000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>3678000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>1706000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1509000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>1910000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>1706000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>965700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>1713900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>2573000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>1586700</v>
       </c>
     </row>
-    <row r="19" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1331,303 +1363,319 @@
       <c r="S19" s="3"/>
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
-    </row>
-    <row r="20" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V19" s="3"/>
+    </row>
+    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-18000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-73000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>66000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>49000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>173000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>179000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>384000</v>
       </c>
-      <c r="J20" s="3" t="s">
+      <c r="K20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>260000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>137000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>319000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>82000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>182000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>120000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>96000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>111200</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>151300</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>100100</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>205400</v>
       </c>
     </row>
-    <row r="21" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>869000</v>
+      </c>
+      <c r="E21" s="3">
         <v>1391000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>804000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-1173000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>1514000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>1512000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>2366000</v>
       </c>
-      <c r="J21" s="3" t="s">
+      <c r="K21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>999000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>1559000</v>
       </c>
-      <c r="M21" s="3" t="s">
+      <c r="N21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>1822000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>1687000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>2090000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>1811000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1173900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1889900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>2745500</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>1792200</v>
       </c>
     </row>
-    <row r="22" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E22" s="3">
+      <c r="E22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F22" s="3">
         <v>97000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>103000</v>
-      </c>
-      <c r="G22" s="3">
-        <v>164000</v>
       </c>
       <c r="H22" s="3">
         <v>164000</v>
       </c>
       <c r="I22" s="3">
+        <v>164000</v>
+      </c>
+      <c r="J22" s="3">
         <v>153000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>163000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>223000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>293000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>547000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>189000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>209000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>216000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>191000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>218500</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>213900</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>194900</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>225200</v>
       </c>
     </row>
-    <row r="23" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>922000</v>
+      </c>
+      <c r="E23" s="3">
         <v>1175000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>704000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-1347000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>1413000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>1263000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>2245000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>663000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>763000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>1159000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>3450000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>1599000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1482000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1814000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1611000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>858400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>1651300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>2478200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>1567000</v>
       </c>
     </row>
-    <row r="24" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>157000</v>
+      </c>
+      <c r="E24" s="3">
         <v>228000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>196000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>158000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>269000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>193000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>311000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>129000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>-32000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>569000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>326000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>152000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>309000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>377000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-29700</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>163000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>584700</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>156700</v>
       </c>
     </row>
-    <row r="25" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1685,126 +1733,135 @@
       <c r="U25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>765000</v>
+      </c>
+      <c r="E26" s="3">
         <v>947000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>508000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-1505000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1144000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1070000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1934000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>534000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>795000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>1158000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>2881000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1273000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1330000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1505000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>1234000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>888200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>1488200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>1893500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>1410300</v>
       </c>
     </row>
-    <row r="27" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>757000</v>
+      </c>
+      <c r="E27" s="3">
         <v>944000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>501000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-1508000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>495000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>1697000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1946000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>512000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>792000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>1152000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>2877000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1272000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1329000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1505000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>1234000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>888200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>1488200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>1893500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>1410300</v>
       </c>
     </row>
-    <row r="28" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1862,49 +1919,52 @@
       <c r="U28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E29" s="3">
-        <v>0</v>
+      <c r="E29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F29" s="3">
         <v>0</v>
       </c>
       <c r="G29" s="3">
+        <v>0</v>
+      </c>
+      <c r="H29" s="3">
         <v>1473000</v>
       </c>
-      <c r="H29" s="3">
+      <c r="I29" s="3">
         <v>-5707000</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>-340000</v>
       </c>
-      <c r="J29" s="3">
-        <v>0</v>
-      </c>
       <c r="K29" s="3">
+        <v>0</v>
+      </c>
+      <c r="L29" s="3">
         <v>-1996000</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>1480000</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>1142000</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>83000</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>-445000</v>
-      </c>
-      <c r="P29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="Q29" s="3" t="s">
         <v>8</v>
@@ -1921,8 +1981,11 @@
       <c r="U29" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="30" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V29" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1980,8 +2043,11 @@
       <c r="U30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2039,126 +2105,135 @@
       <c r="U31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>18000</v>
+      </c>
+      <c r="E32" s="3">
         <v>73000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-66000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-49000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-173000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-179000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-384000</v>
       </c>
-      <c r="J32" s="3" t="s">
+      <c r="K32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-260000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-137000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-319000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-82000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-182000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-120000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-96000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-111200</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-151300</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-100100</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-205400</v>
       </c>
     </row>
-    <row r="33" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>757000</v>
+      </c>
+      <c r="E33" s="3">
         <v>944000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>501000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-1508000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1968000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-4010000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>1606000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>512000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-1204000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>2632000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>4019000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1355000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>884000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1505000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>1234000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>888200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>1488200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>1893500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>1410300</v>
       </c>
     </row>
-    <row r="34" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2216,131 +2291,140 @@
       <c r="U34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>757000</v>
+      </c>
+      <c r="E35" s="3">
         <v>944000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>501000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-1508000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1968000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-4010000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>1606000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>512000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-1204000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>2632000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>4019000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1355000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>884000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1505000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>1234000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>888200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>1488200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>1893500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>1410300</v>
       </c>
     </row>
-    <row r="37" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45107</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44742</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44561</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44377</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44196</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44012</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43830</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>43646</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>43465</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>43281</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>43100</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>42916</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>42735</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>42551</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>42369</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>42185</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>42004</v>
       </c>
     </row>
-    <row r="39" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2362,8 +2446,9 @@
       <c r="S39" s="3"/>
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
-    </row>
-    <row r="40" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V39" s="3"/>
+    </row>
+    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2385,67 +2470,71 @@
       <c r="S40" s="3"/>
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
-    </row>
-    <row r="41" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V40" s="3"/>
+    </row>
+    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>4751000</v>
+      </c>
+      <c r="E41" s="3">
         <v>5920000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>10279000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>5647000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>6259000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>5295000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>7431000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>7785000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>6609000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>6119000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>27051000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>8312000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>20400000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>19024000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>9843000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>11027700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>9676700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>10926700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>8439300</v>
       </c>
     </row>
-    <row r="42" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2503,67 +2592,73 @@
       <c r="U42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1161000</v>
+      </c>
+      <c r="E43" s="3">
         <v>1035000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>2508000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1904000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1613000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1954000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>3171000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>2729000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2054000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2159000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>7990000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>3120000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>5681000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>6610000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>2872000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>4531300</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>2549900</v>
-      </c>
-      <c r="T43" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="U43" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="44" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V43" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2621,8 +2716,11 @@
       <c r="U44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2680,8 +2778,11 @@
       <c r="U45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -2739,185 +2840,197 @@
       <c r="U46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>157419000</v>
+      </c>
+      <c r="E47" s="3">
         <v>149838000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>179110000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>122176000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>170201000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>161057000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>400592000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>377884000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>379715000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>639141000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>913733000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>404637000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>802481000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>796888000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>388381000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>476271200</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>424114700</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>434640800</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>427702600</v>
       </c>
     </row>
-    <row r="48" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>413000</v>
+      </c>
+      <c r="E48" s="3">
         <v>434000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>474000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>440000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>516000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>564000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>916000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>987000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>1090000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1798000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>24624000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>18556000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>33101000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>30513000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>15389000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>19591200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>19067700</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>18755000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>18095300</v>
       </c>
     </row>
-    <row r="49" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>4882000</v>
+      </c>
+      <c r="E49" s="3">
         <v>4565000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>4774000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>909000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>956000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1000000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1031000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1008000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1036000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>723000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>4193000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1769000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1627000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1615000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1680000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>2226200</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>2214700</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>2166100</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>2171400</v>
       </c>
     </row>
-    <row r="50" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2975,8 +3088,11 @@
       <c r="U50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3034,67 +3150,73 @@
       <c r="U51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>156000</v>
+      </c>
+      <c r="E52" s="3">
         <v>168000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>140000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>378000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>266000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>336048000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>4858000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>4259000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>4075000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>284138000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>29949000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>14459000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>5330000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>8276000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>6027000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>4914000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>3678200</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>3713300</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>4726000</v>
       </c>
     </row>
-    <row r="53" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3152,67 +3274,73 @@
       <c r="U53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>174066000</v>
+      </c>
+      <c r="E54" s="3">
         <v>165458000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>160249000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>166888000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>199102000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>525121000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>516097000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>463165000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>454214000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>705945000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>647810000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>501170000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>493941000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>481130000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>470498000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>567962500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>504748400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>497616300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>486164100</v>
       </c>
     </row>
-    <row r="55" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3234,8 +3362,9 @@
       <c r="S55" s="3"/>
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
-    </row>
-    <row r="56" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V55" s="3"/>
+    </row>
+    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3257,8 +3386,9 @@
       <c r="S56" s="3"/>
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
-    </row>
-    <row r="57" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V56" s="3"/>
+    </row>
+    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -3316,43 +3446,46 @@
       <c r="U57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>699000</v>
+      </c>
+      <c r="E58" s="3">
         <v>529000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>501000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>544000</v>
-      </c>
-      <c r="G58" s="3">
-        <v>500000</v>
       </c>
       <c r="H58" s="3">
         <v>500000</v>
       </c>
       <c r="I58" s="3">
+        <v>500000</v>
+      </c>
+      <c r="J58" s="3">
         <v>501000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>506000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>549000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>841000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>716000</v>
-      </c>
-      <c r="N58" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="O58" s="3" t="s">
         <v>8</v>
@@ -3363,8 +3496,8 @@
       <c r="Q58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R58" s="3">
-        <v>0</v>
+      <c r="R58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="S58" s="3">
         <v>0</v>
@@ -3375,67 +3508,73 @@
       <c r="U58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>149497000</v>
+      </c>
+      <c r="E59" s="3">
         <v>141586000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>269414000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>141801000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>171008000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>165465000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>477515000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>429139000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>419599000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>393980000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>830364000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>453226000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>816205000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>866408000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>369166000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>507721400</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>399974500</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>448806800</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>360479200</v>
       </c>
     </row>
-    <row r="60" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -3493,126 +3632,135 @@
       <c r="U60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>4175000</v>
+      </c>
+      <c r="E61" s="3">
         <v>4222000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>4575000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>4576000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>6488000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>6799000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>8576000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>8223000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>7669000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>11004000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>15334000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>11570000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>11787000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>12046000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>10452000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>13166000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>10829700</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>11157200</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>10086600</v>
       </c>
     </row>
-    <row r="62" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1250000</v>
+      </c>
+      <c r="E62" s="3">
         <v>1214000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1139000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>2699000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>2862000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>335495000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>6075000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>5278000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>5237000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>277443000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>33150000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>16420000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>9392000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>11366000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>6761000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>6938500</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>5195100</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>5695100</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>5650300</v>
       </c>
     </row>
-    <row r="63" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3670,8 +3818,11 @@
       <c r="U63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3729,8 +3880,11 @@
       <c r="U64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3788,67 +3942,73 @@
       <c r="U65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>156243000</v>
+      </c>
+      <c r="E66" s="3">
         <v>148299000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>143518000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>150779000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>182014000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>509408000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>495219000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>444055000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>434737000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>680908000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>625842000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>485288000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>477854000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>465681000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>455832000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>549081000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>487851100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>481677800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>470611500</v>
       </c>
     </row>
-    <row r="67" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3870,8 +4030,9 @@
       <c r="S67" s="3"/>
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
-    </row>
-    <row r="68" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V67" s="3"/>
+    </row>
+    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3929,8 +4090,11 @@
       <c r="U68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3988,8 +4152,11 @@
       <c r="U69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4047,8 +4214,11 @@
       <c r="U70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4106,67 +4276,73 @@
       <c r="U71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3" t="s">
+      <c r="D72" s="3">
+        <v>11928000</v>
+      </c>
+      <c r="E72" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>10810000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>9997000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>10216000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>10180000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>14424000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>13420000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>13575000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>22597000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>21817000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>12954000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>12326000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>11700000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>10942000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>13160800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>13611800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>12624100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>11572000</v>
       </c>
     </row>
-    <row r="73" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4224,8 +4400,11 @@
       <c r="U73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4283,8 +4462,11 @@
       <c r="U74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4342,67 +4524,73 @@
       <c r="U75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>17823000</v>
+      </c>
+      <c r="E76" s="3">
         <v>17159000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>16731000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>16109000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>17088000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>15713000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>20878000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>19110000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>19477000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>25037000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>21968000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>15882000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>16087000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>15449000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>14666000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>18881500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>16897300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>15938400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>15552600</v>
       </c>
     </row>
-    <row r="77" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4460,131 +4648,140 @@
       <c r="U77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:21" x14ac:dyDescent="0.2">
+      <c r="V77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:21" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45107</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44742</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44561</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44377</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44196</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44012</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43830</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>43646</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>43465</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>43281</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>43100</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>42916</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>42735</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>42551</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>42369</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>42185</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>42004</v>
       </c>
     </row>
-    <row r="81" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>757000</v>
+      </c>
+      <c r="E81" s="3">
         <v>944000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>501000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-1508000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1968000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-4010000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>1606000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>512000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-1204000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>2632000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>4019000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1355000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>884000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1505000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>1234000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>888200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>1488200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>1893500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>1410300</v>
       </c>
     </row>
-    <row r="82" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4606,8 +4803,9 @@
       <c r="S82" s="3"/>
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
-    </row>
-    <row r="83" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V82" s="3"/>
+    </row>
+    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4665,8 +4863,11 @@
       <c r="U83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4724,8 +4925,11 @@
       <c r="U84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4783,8 +4987,11 @@
       <c r="U85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4842,8 +5049,11 @@
       <c r="U86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4901,8 +5111,11 @@
       <c r="U87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4960,67 +5173,73 @@
       <c r="U88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>-435000</v>
+      </c>
+      <c r="E89" s="3">
         <v>1267000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>-638000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>1716000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>-2111000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>768000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>325000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>2109000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-5016000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-746000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>2745000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>980000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1530000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>90000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1398000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1038100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>174800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>3159000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>1638100</v>
       </c>
     </row>
-    <row r="90" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5042,67 +5261,71 @@
       <c r="S90" s="3"/>
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
-    </row>
-    <row r="91" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V90" s="3"/>
+    </row>
+    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-26000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-18000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-20000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-14000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-17000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-19000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-14000</v>
-      </c>
-      <c r="J91" s="3">
-        <v>-43000</v>
       </c>
       <c r="K91" s="3">
         <v>-43000</v>
       </c>
       <c r="L91" s="3">
+        <v>-43000</v>
+      </c>
+      <c r="M91" s="3">
         <v>-16000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-100000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-59000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-78000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-56000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-316000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-41400</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-216500</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-118500</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-160600</v>
       </c>
     </row>
-    <row r="92" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5160,8 +5383,11 @@
       <c r="U92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5219,67 +5445,73 @@
       <c r="U93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-418000</v>
+      </c>
+      <c r="E94" s="3">
         <v>58000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>25000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-64000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>66000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-792000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-417000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-776000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-236000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-88000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-431000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-191000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>59000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>757000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-215000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-431800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-538700</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-73700</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>51400</v>
       </c>
     </row>
-    <row r="95" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5301,67 +5533,71 @@
       <c r="S95" s="3"/>
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
-    </row>
-    <row r="96" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V95" s="3"/>
+    </row>
+    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>-172000</v>
+      </c>
+      <c r="E96" s="3">
         <v>-361000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>-154000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>-320000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>-138000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>-283000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>-140000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>-674000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-764000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-870000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-1244000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-840000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-373000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-786000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-332000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-1208800</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-410900</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-867800</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-375300</v>
       </c>
     </row>
-    <row r="97" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5419,8 +5655,11 @@
       <c r="U97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5478,8 +5717,11 @@
       <c r="U98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5537,181 +5779,193 @@
       <c r="U99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:21" x14ac:dyDescent="0.2">
+      <c r="V99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-331000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-879000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-293000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-2227000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>1760000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-495000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>67000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>145000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-1183000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1274000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>214000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-680000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-715000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-987000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>41000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-532600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-598700</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-283100</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-1173300</v>
       </c>
     </row>
-    <row r="101" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>15000</v>
+      </c>
+      <c r="E101" s="3">
         <v>-40000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>5000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-180000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-1000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-43000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>129000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-59000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>193000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>10000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>304000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>31000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-77000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-32000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>311000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>893300</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>289600</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-314700</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>150100</v>
       </c>
     </row>
-    <row r="102" spans="3:21" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-1169000</v>
+      </c>
+      <c r="E102" s="3">
         <v>406000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-901000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-755000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-286000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-562000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-366000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>1419000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-6184000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-2293000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>2547000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>140000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>797000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-172000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>1535000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>967000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-673000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>2487400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>666300</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/PUK_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PUK_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="92">
   <si>
     <t>PUK</t>
   </si>
@@ -656,151 +656,157 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:V102"/>
+  <dimension ref="A5:W102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="22" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="23" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45107</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44742</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44561</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44377</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44196</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44012</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>43830</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>43646</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>43465</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>43281</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>43100</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>42916</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>42735</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>42551</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>42369</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>42185</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>42004</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>5073000</v>
+      </c>
+      <c r="E8" s="3">
         <v>5324000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>5336000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>4754000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>2243000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>14808000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>11692000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>42311000</v>
       </c>
-      <c r="K8" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L8" s="3">
+      <c r="L8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M8" s="3">
         <v>41197000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>52539000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>35845000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>16019000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>43466000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>42924000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>36301000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>45947800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>20902900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>33287100</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>38844000</v>
       </c>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -810,59 +816,62 @@
       <c r="E9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F9" s="3">
+      <c r="F9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G9" s="3">
         <v>1205000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1120000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1063000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1026000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>647000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1433000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2068000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2109000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>6103000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>3186000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1792000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1920000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1987000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>2197800</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>2210800</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>2080500</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>4498200</v>
       </c>
     </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
@@ -872,59 +881,62 @@
       <c r="E10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F10" s="3">
+      <c r="F10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G10" s="3">
         <v>3549000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1123000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>13745000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>10666000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>41664000</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L10" s="3">
+      <c r="L10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M10" s="3">
         <v>39129000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>50430000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>29742000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>12833000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>41674000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>41004000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>34314000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>43750000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>18692100</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>31206600</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>34345800</v>
       </c>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -947,8 +959,9 @@
       <c r="T11" s="3"/>
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W11" s="3"/>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1009,8 +1022,11 @@
       <c r="V12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1071,70 +1087,76 @@
       <c r="V13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>69000</v>
+      </c>
+      <c r="E14" s="3">
         <v>22000</v>
       </c>
-      <c r="E14" s="3">
-        <v>0</v>
-      </c>
       <c r="F14" s="3">
+        <v>0</v>
+      </c>
+      <c r="G14" s="3">
         <v>7000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-62000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>-21000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>56000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>30000</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
-      </c>
       <c r="L14" s="3">
+        <v>0</v>
+      </c>
+      <c r="M14" s="3">
         <v>159000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>-17000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>182000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>570000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>-162000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>-66000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>238000</v>
       </c>
-      <c r="S14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="T14" s="3">
-        <v>0</v>
+      <c r="T14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="U14" s="3">
         <v>0</v>
       </c>
       <c r="V14" s="3">
+        <v>0</v>
+      </c>
+      <c r="W14" s="3">
         <v>2600</v>
       </c>
     </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1144,33 +1166,33 @@
       <c r="E15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F15" s="3">
+      <c r="F15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G15" s="3">
         <v>74000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>71000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>61000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>85000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>77000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>109000</v>
       </c>
-      <c r="L15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M15" s="3">
+      <c r="M15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N15" s="3">
         <v>107000</v>
       </c>
-      <c r="N15" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="O15" s="3" t="s">
         <v>8</v>
       </c>
@@ -1180,11 +1202,11 @@
       <c r="Q15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R15" s="3">
-        <v>0</v>
-      </c>
-      <c r="S15" s="3" t="s">
-        <v>8</v>
+      <c r="R15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S15" s="3">
+        <v>0</v>
       </c>
       <c r="T15" s="3" t="s">
         <v>8</v>
@@ -1195,8 +1217,11 @@
       <c r="V15" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.2">
+      <c r="W15" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1216,132 +1241,139 @@
       <c r="T16" s="3"/>
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
-    </row>
-    <row r="17" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W16" s="3"/>
+    </row>
+    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>4436000</v>
+      </c>
+      <c r="E17" s="3">
         <v>4384000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>4088000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>4019000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>3536000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>13404000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>10444000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>40297000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>-6757000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>40471000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>51224000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>32167000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>14313000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>41957000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>41014000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>34595000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>44982000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>19189000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>30714100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>37257300</v>
       </c>
     </row>
-    <row r="18" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>637000</v>
+      </c>
+      <c r="E18" s="3">
         <v>940000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>1248000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>735000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>-1293000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>1404000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>1248000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>2014000</v>
       </c>
-      <c r="K18" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L18" s="3">
+      <c r="L18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M18" s="3">
         <v>726000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>1315000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>3678000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>1706000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>1509000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>1910000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>1706000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>965700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>1713900</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>2573000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>1586700</v>
       </c>
     </row>
-    <row r="19" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1364,132 +1396,139 @@
       <c r="T19" s="3"/>
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
-    </row>
-    <row r="20" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W19" s="3"/>
+    </row>
+    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-243000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-18000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-73000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>66000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>49000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>173000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>179000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>384000</v>
       </c>
-      <c r="K20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L20" s="3">
+      <c r="L20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M20" s="3">
         <v>260000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>137000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>319000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>82000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>182000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>120000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>96000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>111200</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>151300</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>100100</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>205400</v>
       </c>
     </row>
-    <row r="21" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>599000</v>
+      </c>
+      <c r="E21" s="3">
         <v>869000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>1391000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>804000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>-1173000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>1514000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>1512000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>2366000</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L21" s="3">
+      <c r="L21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M21" s="3">
         <v>999000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>1559000</v>
       </c>
-      <c r="N21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O21" s="3">
+      <c r="O21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P21" s="3">
         <v>1822000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>1687000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>2090000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>1811000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>1173900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>1889900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>2745500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>1792200</v>
       </c>
     </row>
-    <row r="22" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1499,183 +1538,192 @@
       <c r="E22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F22" s="3">
+      <c r="F22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G22" s="3">
         <v>97000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>103000</v>
-      </c>
-      <c r="H22" s="3">
-        <v>164000</v>
       </c>
       <c r="I22" s="3">
         <v>164000</v>
       </c>
       <c r="J22" s="3">
+        <v>164000</v>
+      </c>
+      <c r="K22" s="3">
         <v>153000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>163000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>223000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>293000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>547000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>189000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>209000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>216000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>191000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>218500</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>213900</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>194900</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>225200</v>
       </c>
     </row>
-    <row r="23" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>394000</v>
+      </c>
+      <c r="E23" s="3">
         <v>922000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>1175000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>704000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-1347000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>1413000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>1263000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>2245000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>663000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>763000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>1159000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>3450000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>1599000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>1482000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>1814000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>1611000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>858400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>1651300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>2478200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>1567000</v>
       </c>
     </row>
-    <row r="24" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>212000</v>
+      </c>
+      <c r="E24" s="3">
         <v>157000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>228000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>196000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>158000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>269000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>193000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>311000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>129000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>-32000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>1000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>569000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>326000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>152000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>309000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>377000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-29700</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>163000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>584700</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>156700</v>
       </c>
     </row>
-    <row r="25" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1736,132 +1784,141 @@
       <c r="V25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>182000</v>
+      </c>
+      <c r="E26" s="3">
         <v>765000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>947000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>508000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-1505000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1144000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>1070000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>1934000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>534000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>795000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>1158000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>2881000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1273000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1330000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>1505000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>1234000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>888200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>1488200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>1893500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>1410300</v>
       </c>
     </row>
-    <row r="27" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>120000</v>
+      </c>
+      <c r="E27" s="3">
         <v>757000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>944000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>501000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-1508000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>495000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>1697000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>1946000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>512000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>792000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>1152000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>2877000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1272000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1329000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>1505000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>1234000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>888200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>1488200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>1893500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>1410300</v>
       </c>
     </row>
-    <row r="28" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1922,8 +1979,11 @@
       <c r="V28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -1933,42 +1993,42 @@
       <c r="E29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F29" s="3">
-        <v>0</v>
+      <c r="F29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="G29" s="3">
         <v>0</v>
       </c>
       <c r="H29" s="3">
+        <v>0</v>
+      </c>
+      <c r="I29" s="3">
         <v>1473000</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>-5707000</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>-340000</v>
       </c>
-      <c r="K29" s="3">
-        <v>0</v>
-      </c>
       <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3">
         <v>-1996000</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>1480000</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>1142000</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>83000</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>-445000</v>
       </c>
-      <c r="Q29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R29" s="3" t="s">
         <v>8</v>
       </c>
@@ -1984,8 +2044,11 @@
       <c r="V29" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="30" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W29" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2046,8 +2109,11 @@
       <c r="V30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2108,132 +2174,141 @@
       <c r="V31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>243000</v>
+      </c>
+      <c r="E32" s="3">
         <v>18000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>73000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-66000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-49000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-173000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-179000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-384000</v>
       </c>
-      <c r="K32" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L32" s="3">
+      <c r="L32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M32" s="3">
         <v>-260000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-137000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-319000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-82000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-182000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-120000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-96000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-111200</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-151300</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-100100</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-205400</v>
       </c>
     </row>
-    <row r="33" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>120000</v>
+      </c>
+      <c r="E33" s="3">
         <v>757000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>944000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>501000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-1508000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>1968000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-4010000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>1606000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>512000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-1204000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>2632000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>4019000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1355000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>884000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>1505000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>1234000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>888200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>1488200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>1893500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>1410300</v>
       </c>
     </row>
-    <row r="34" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2294,137 +2369,146 @@
       <c r="V34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>120000</v>
+      </c>
+      <c r="E35" s="3">
         <v>757000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>944000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>501000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-1508000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>1968000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-4010000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>1606000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>512000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-1204000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>2632000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>4019000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1355000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>884000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>1505000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>1234000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>888200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>1488200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>1893500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>1410300</v>
       </c>
     </row>
-    <row r="37" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45107</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44742</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44561</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44377</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44196</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44012</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>43830</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>43646</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>43465</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>43281</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>43100</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>42916</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>42735</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>42551</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>42369</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>42185</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>42004</v>
       </c>
     </row>
-    <row r="39" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2447,8 +2531,9 @@
       <c r="T39" s="3"/>
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
-    </row>
-    <row r="40" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W39" s="3"/>
+    </row>
+    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2471,70 +2556,74 @@
       <c r="T40" s="3"/>
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
-    </row>
-    <row r="41" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W40" s="3"/>
+    </row>
+    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>5978000</v>
+      </c>
+      <c r="E41" s="3">
         <v>4751000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>5920000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>10279000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>5647000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>6259000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>5295000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>7431000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>7785000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>6609000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>6119000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>27051000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>8312000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>20400000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>19024000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>9843000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>11027700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>9676700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>10926700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>8439300</v>
       </c>
     </row>
-    <row r="42" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2595,70 +2684,76 @@
       <c r="V42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2440000</v>
+      </c>
+      <c r="E43" s="3">
         <v>1161000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1035000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>2508000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1904000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1613000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1954000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>3171000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2729000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2054000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2159000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>7990000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>3120000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>5681000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>6610000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>2872000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>4531300</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>2549900</v>
       </c>
-      <c r="U43" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="V43" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="44" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W43" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2719,8 +2814,11 @@
       <c r="V44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -2781,8 +2879,11 @@
       <c r="V45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
@@ -2843,194 +2944,206 @@
       <c r="V46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>156417000</v>
+      </c>
+      <c r="E47" s="3">
         <v>157419000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>149838000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>179110000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>122176000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>170201000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>161057000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>400592000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>377884000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>379715000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>639141000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>913733000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>404637000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>802481000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>796888000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>388381000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>476271200</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>424114700</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>434640800</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>427702600</v>
       </c>
     </row>
-    <row r="48" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>393000</v>
+      </c>
+      <c r="E48" s="3">
         <v>413000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>434000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>474000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>440000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>516000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>564000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>916000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>987000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>1090000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>1798000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>24624000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>18556000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>33101000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>30513000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>15389000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>19591200</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>19067700</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>18755000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>18095300</v>
       </c>
     </row>
-    <row r="49" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>4577000</v>
+      </c>
+      <c r="E49" s="3">
         <v>4882000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>4565000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>4774000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>909000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>956000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1000000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1031000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1008000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1036000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>723000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>4193000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1769000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1627000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1615000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>1680000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>2226200</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>2214700</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>2166100</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>2171400</v>
       </c>
     </row>
-    <row r="50" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3091,8 +3204,11 @@
       <c r="V50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3153,70 +3269,76 @@
       <c r="V51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>446000</v>
+      </c>
+      <c r="E52" s="3">
         <v>156000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>168000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>140000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>378000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>266000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>336048000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>4858000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>4259000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>4075000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>284138000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>29949000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>14459000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>5330000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>8276000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>6027000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>4914000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>3678200</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>3713300</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>4726000</v>
       </c>
     </row>
-    <row r="53" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3277,70 +3399,76 @@
       <c r="V53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>174687000</v>
+      </c>
+      <c r="E54" s="3">
         <v>174066000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>165458000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>160249000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>166888000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>199102000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>525121000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>516097000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>463165000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>454214000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>705945000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>647810000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>501170000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>493941000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>481130000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>470498000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>567962500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>504748400</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>497616300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>486164100</v>
       </c>
     </row>
-    <row r="55" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3363,8 +3491,9 @@
       <c r="T55" s="3"/>
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
-    </row>
-    <row r="56" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W55" s="3"/>
+    </row>
+    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3387,8 +3516,9 @@
       <c r="T56" s="3"/>
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
-    </row>
-    <row r="57" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W56" s="3"/>
+    </row>
+    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
@@ -3449,47 +3579,50 @@
       <c r="V57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>660000</v>
+      </c>
+      <c r="E58" s="3">
         <v>699000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>529000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>501000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>544000</v>
-      </c>
-      <c r="H58" s="3">
-        <v>500000</v>
       </c>
       <c r="I58" s="3">
         <v>500000</v>
       </c>
       <c r="J58" s="3">
+        <v>500000</v>
+      </c>
+      <c r="K58" s="3">
         <v>501000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>506000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>549000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>841000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>716000</v>
       </c>
-      <c r="O58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="P58" s="3" t="s">
         <v>8</v>
       </c>
@@ -3499,8 +3632,8 @@
       <c r="R58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S58" s="3">
-        <v>0</v>
+      <c r="S58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="T58" s="3">
         <v>0</v>
@@ -3511,70 +3644,76 @@
       <c r="V58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>150420000</v>
+      </c>
+      <c r="E59" s="3">
         <v>149497000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>141586000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>269414000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>141801000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>171008000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>165465000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>477515000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>429139000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>419599000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>393980000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>830364000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>453226000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>816205000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>866408000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>369166000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>507721400</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>399974500</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>448806800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>360479200</v>
       </c>
     </row>
-    <row r="60" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
@@ -3635,132 +3774,141 @@
       <c r="V60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>4231000</v>
+      </c>
+      <c r="E61" s="3">
         <v>4175000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>4222000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>4575000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>4576000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>6488000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>6799000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>8576000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>8223000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>7669000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>11004000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>15334000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>11570000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>11787000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>12046000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>10452000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>13166000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>10829700</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>11157200</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>10086600</v>
       </c>
     </row>
-    <row r="62" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1577000</v>
+      </c>
+      <c r="E62" s="3">
         <v>1250000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1214000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1139000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>2699000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>2862000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>335495000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>6075000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>5278000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>5237000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>277443000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>33150000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>16420000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>9392000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>11366000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>6761000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>6938500</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>5195100</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>5695100</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>5650300</v>
       </c>
     </row>
-    <row r="63" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3821,8 +3969,11 @@
       <c r="V63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3883,8 +4034,11 @@
       <c r="V64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3945,70 +4099,76 @@
       <c r="V65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>158516000</v>
+      </c>
+      <c r="E66" s="3">
         <v>156243000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>148299000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>143518000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>150779000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>182014000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>509408000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>495219000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>444055000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>434737000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>680908000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>625842000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>485288000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>477854000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>465681000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>455832000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>549081000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>487851100</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>481677800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>470611500</v>
       </c>
     </row>
-    <row r="67" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4031,8 +4191,9 @@
       <c r="T67" s="3"/>
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
-    </row>
-    <row r="68" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W67" s="3"/>
+    </row>
+    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4093,8 +4254,11 @@
       <c r="V68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4155,8 +4319,11 @@
       <c r="V69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4217,8 +4384,11 @@
       <c r="V70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4279,70 +4449,76 @@
       <c r="V71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3">
+      <c r="D72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E72" s="3">
         <v>11928000</v>
       </c>
-      <c r="E72" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F72" s="3">
+      <c r="F72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G72" s="3">
         <v>10810000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>9997000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>10216000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>10180000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>14424000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>13420000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>13575000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>22597000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>21817000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>12954000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>12326000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>11700000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>10942000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>13160800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>13611800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>12624100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>11572000</v>
       </c>
     </row>
-    <row r="73" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4403,8 +4579,11 @@
       <c r="V73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4465,8 +4644,11 @@
       <c r="V74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4527,70 +4709,76 @@
       <c r="V75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>16171000</v>
+      </c>
+      <c r="E76" s="3">
         <v>17823000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>17159000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>16731000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>16109000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>17088000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>15713000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>20878000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>19110000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>19477000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>25037000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>21968000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>15882000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>16087000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>15449000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>14666000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>18881500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>16897300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>15938400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>15552600</v>
       </c>
     </row>
-    <row r="77" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4651,137 +4839,146 @@
       <c r="V77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:22" x14ac:dyDescent="0.2">
+      <c r="W77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:22" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45107</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44742</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44561</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44377</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44196</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44012</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>43830</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>43646</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>43465</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>43281</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>43100</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>42916</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>42735</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>42551</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>42369</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>42185</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>42004</v>
       </c>
     </row>
-    <row r="81" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>120000</v>
+      </c>
+      <c r="E81" s="3">
         <v>757000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>944000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>501000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-1508000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>1968000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-4010000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>1606000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>512000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-1204000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>2632000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>4019000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1355000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>884000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>1505000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>1234000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>888200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>1488200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>1893500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>1410300</v>
       </c>
     </row>
-    <row r="82" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -4804,8 +5001,9 @@
       <c r="T82" s="3"/>
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
-    </row>
-    <row r="83" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W82" s="3"/>
+    </row>
+    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -4866,8 +5064,11 @@
       <c r="V83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -4928,8 +5129,11 @@
       <c r="V84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4990,8 +5194,11 @@
       <c r="V85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5052,8 +5259,11 @@
       <c r="V86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5114,8 +5324,11 @@
       <c r="V87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5176,70 +5389,76 @@
       <c r="V88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>2173000</v>
+      </c>
+      <c r="E89" s="3">
         <v>-435000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>1267000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>-638000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>1716000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-2111000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>768000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>325000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>2109000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-5016000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-746000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>2745000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>980000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>1530000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>90000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1398000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>1038100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>174800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>3159000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>1638100</v>
       </c>
     </row>
-    <row r="90" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5262,70 +5481,74 @@
       <c r="T90" s="3"/>
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
-    </row>
-    <row r="91" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W90" s="3"/>
+    </row>
+    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-27000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-26000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-18000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-20000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-14000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-17000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-19000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-14000</v>
-      </c>
-      <c r="K91" s="3">
-        <v>-43000</v>
       </c>
       <c r="L91" s="3">
         <v>-43000</v>
       </c>
       <c r="M91" s="3">
+        <v>-43000</v>
+      </c>
+      <c r="N91" s="3">
         <v>-16000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-100000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-59000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-78000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-56000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-316000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-41400</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-216500</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-118500</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-160600</v>
       </c>
     </row>
-    <row r="92" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5386,8 +5609,11 @@
       <c r="V92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5448,70 +5674,76 @@
       <c r="V93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-270000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-418000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>58000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>25000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-64000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>66000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-792000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-417000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-776000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-236000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-88000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-431000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-191000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>59000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>757000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-215000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-431800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-538700</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-73700</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>51400</v>
       </c>
     </row>
-    <row r="95" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5534,70 +5766,74 @@
       <c r="T95" s="3"/>
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
-    </row>
-    <row r="96" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W95" s="3"/>
+    </row>
+    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>-390000</v>
+      </c>
+      <c r="E96" s="3">
         <v>-172000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>-361000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>-154000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>-320000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>-138000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>-283000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>-140000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-674000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-764000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-870000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-1244000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-840000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-373000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-786000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-332000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="T96" s="3">
         <v>-1208800</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-410900</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-867800</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-375300</v>
       </c>
     </row>
-    <row r="97" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5658,8 +5894,11 @@
       <c r="V97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5720,8 +5959,11 @@
       <c r="V98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -5782,190 +6024,202 @@
       <c r="V99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:22" x14ac:dyDescent="0.2">
+      <c r="W99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-571000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-331000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-879000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-293000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-2227000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>1760000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-495000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>67000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>145000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-1183000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-1274000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>214000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-680000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-715000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-987000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>41000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-532600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-598700</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-283100</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-1173300</v>
       </c>
     </row>
-    <row r="101" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-105000</v>
+      </c>
+      <c r="E101" s="3">
         <v>15000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-40000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>5000</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-180000</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-1000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-43000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>129000</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-59000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>193000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>10000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>304000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>31000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-77000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-32000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>311000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>893300</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>289600</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-314700</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>150100</v>
       </c>
     </row>
-    <row r="102" spans="3:22" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>1227000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-1169000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>406000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-901000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-755000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-286000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-562000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-366000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>1419000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-6184000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-2293000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>2547000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>140000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>797000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-172000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>1535000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>967000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-673000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>2487400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>666300</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/PUK_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PUK_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="161" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="92">
   <si>
     <t>PUK</t>
   </si>
@@ -684,22 +684,22 @@
         <v>45473</v>
       </c>
       <c r="E7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
+        <v>45199</v>
+      </c>
+      <c r="H7" s="2">
         <v>45107</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
+        <v>45016</v>
+      </c>
+      <c r="J7" s="2">
         <v>44926</v>
-      </c>
-      <c r="H7" s="2">
-        <v>44742</v>
-      </c>
-      <c r="I7" s="2">
-        <v>44561</v>
-      </c>
-      <c r="J7" s="2">
-        <v>44377</v>
       </c>
       <c r="K7" s="2">
         <v>44196</v>
@@ -746,25 +746,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>5073000</v>
+        <v>2662500</v>
       </c>
       <c r="E8" s="3">
-        <v>5324000</v>
+        <v>2662500</v>
       </c>
       <c r="F8" s="3">
-        <v>5336000</v>
+        <v>2809500</v>
       </c>
       <c r="G8" s="3">
-        <v>4754000</v>
+        <v>2809500</v>
       </c>
       <c r="H8" s="3">
-        <v>2243000</v>
+        <v>2709500</v>
       </c>
       <c r="I8" s="3">
-        <v>14808000</v>
+        <v>2709500</v>
       </c>
       <c r="J8" s="3">
-        <v>11692000</v>
+        <v>2797500</v>
       </c>
       <c r="K8" s="3">
         <v>42311000</v>
@@ -810,26 +810,26 @@
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="D9" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>8</v>
+      <c r="D9" s="3">
+        <v>1945000</v>
+      </c>
+      <c r="E9" s="3">
+        <v>1945000</v>
+      </c>
+      <c r="F9" s="3">
+        <v>1856000</v>
       </c>
       <c r="G9" s="3">
-        <v>1205000</v>
+        <v>1856000</v>
       </c>
       <c r="H9" s="3">
-        <v>1120000</v>
+        <v>1786000</v>
       </c>
       <c r="I9" s="3">
-        <v>1063000</v>
+        <v>1786000</v>
       </c>
       <c r="J9" s="3">
-        <v>1026000</v>
+        <v>1735500</v>
       </c>
       <c r="K9" s="3">
         <v>647000</v>
@@ -875,26 +875,26 @@
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>8</v>
+      <c r="D10" s="3">
+        <v>717500</v>
+      </c>
+      <c r="E10" s="3">
+        <v>717500</v>
+      </c>
+      <c r="F10" s="3">
+        <v>953500</v>
       </c>
       <c r="G10" s="3">
-        <v>3549000</v>
+        <v>953500</v>
       </c>
       <c r="H10" s="3">
-        <v>1123000</v>
+        <v>923500</v>
       </c>
       <c r="I10" s="3">
-        <v>13745000</v>
+        <v>923500</v>
       </c>
       <c r="J10" s="3">
-        <v>10666000</v>
+        <v>1062000</v>
       </c>
       <c r="K10" s="3">
         <v>41664000</v>
@@ -1096,25 +1096,25 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>69000</v>
+        <v>34500</v>
       </c>
       <c r="E14" s="3">
-        <v>22000</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0</v>
-      </c>
-      <c r="G14" s="3">
-        <v>7000</v>
-      </c>
-      <c r="H14" s="3">
-        <v>-62000</v>
-      </c>
-      <c r="I14" s="3">
-        <v>-21000</v>
-      </c>
-      <c r="J14" s="3">
-        <v>56000</v>
+        <v>34500</v>
+      </c>
+      <c r="F14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K14" s="3">
         <v>30000</v>
@@ -1160,26 +1160,26 @@
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>8</v>
+      <c r="D15" s="3">
+        <v>102500</v>
+      </c>
+      <c r="E15" s="3">
+        <v>102500</v>
+      </c>
+      <c r="F15" s="3">
+        <v>106500</v>
       </c>
       <c r="G15" s="3">
-        <v>74000</v>
+        <v>106500</v>
       </c>
       <c r="H15" s="3">
-        <v>71000</v>
+        <v>108000</v>
       </c>
       <c r="I15" s="3">
-        <v>61000</v>
+        <v>108000</v>
       </c>
       <c r="J15" s="3">
-        <v>85000</v>
+        <v>169000</v>
       </c>
       <c r="K15" s="3">
         <v>77000</v>
@@ -1248,25 +1248,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>4436000</v>
+        <v>1945000</v>
       </c>
       <c r="E17" s="3">
-        <v>4384000</v>
+        <v>1945000</v>
       </c>
       <c r="F17" s="3">
-        <v>4088000</v>
+        <v>1856000</v>
       </c>
       <c r="G17" s="3">
-        <v>4019000</v>
+        <v>1856000</v>
       </c>
       <c r="H17" s="3">
-        <v>3536000</v>
+        <v>1786000</v>
       </c>
       <c r="I17" s="3">
-        <v>13404000</v>
+        <v>1786000</v>
       </c>
       <c r="J17" s="3">
-        <v>10444000</v>
+        <v>1735500</v>
       </c>
       <c r="K17" s="3">
         <v>40297000</v>
@@ -1313,25 +1313,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>637000</v>
+        <v>717500</v>
       </c>
       <c r="E18" s="3">
-        <v>940000</v>
+        <v>717500</v>
       </c>
       <c r="F18" s="3">
-        <v>1248000</v>
+        <v>953500</v>
       </c>
       <c r="G18" s="3">
-        <v>735000</v>
+        <v>953500</v>
       </c>
       <c r="H18" s="3">
-        <v>-1293000</v>
+        <v>923500</v>
       </c>
       <c r="I18" s="3">
-        <v>1404000</v>
+        <v>923500</v>
       </c>
       <c r="J18" s="3">
-        <v>1248000</v>
+        <v>1062000</v>
       </c>
       <c r="K18" s="3">
         <v>2014000</v>
@@ -1403,25 +1403,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-243000</v>
+        <v>387500</v>
       </c>
       <c r="E20" s="3">
-        <v>-18000</v>
+        <v>387500</v>
       </c>
       <c r="F20" s="3">
-        <v>-73000</v>
+        <v>250000</v>
       </c>
       <c r="G20" s="3">
-        <v>66000</v>
+        <v>250000</v>
       </c>
       <c r="H20" s="3">
-        <v>49000</v>
+        <v>259500</v>
       </c>
       <c r="I20" s="3">
-        <v>173000</v>
+        <v>259500</v>
       </c>
       <c r="J20" s="3">
-        <v>179000</v>
+        <v>480000</v>
       </c>
       <c r="K20" s="3">
         <v>384000</v>
@@ -1468,25 +1468,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>599000</v>
+        <v>432500</v>
       </c>
       <c r="E21" s="3">
-        <v>869000</v>
+        <v>432500</v>
       </c>
       <c r="F21" s="3">
-        <v>1391000</v>
+        <v>810000</v>
       </c>
       <c r="G21" s="3">
-        <v>804000</v>
+        <v>810000</v>
       </c>
       <c r="H21" s="3">
-        <v>-1173000</v>
+        <v>772000</v>
       </c>
       <c r="I21" s="3">
-        <v>1514000</v>
+        <v>772000</v>
       </c>
       <c r="J21" s="3">
-        <v>1512000</v>
+        <v>751000</v>
       </c>
       <c r="K21" s="3">
         <v>2366000</v>
@@ -1532,26 +1532,26 @@
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E22" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>8</v>
+      <c r="D22" s="3">
+        <v>42500</v>
+      </c>
+      <c r="E22" s="3">
+        <v>42500</v>
+      </c>
+      <c r="F22" s="3">
+        <v>189000</v>
       </c>
       <c r="G22" s="3">
-        <v>97000</v>
+        <v>189000</v>
       </c>
       <c r="H22" s="3">
-        <v>103000</v>
+        <v>42500</v>
       </c>
       <c r="I22" s="3">
-        <v>164000</v>
+        <v>42500</v>
       </c>
       <c r="J22" s="3">
-        <v>164000</v>
+        <v>180000</v>
       </c>
       <c r="K22" s="3">
         <v>153000</v>
@@ -1598,25 +1598,25 @@
         <v>18</v>
       </c>
       <c r="D23" s="3">
-        <v>394000</v>
+        <v>253000</v>
       </c>
       <c r="E23" s="3">
-        <v>922000</v>
+        <v>253000</v>
       </c>
       <c r="F23" s="3">
-        <v>1175000</v>
+        <v>514500</v>
       </c>
       <c r="G23" s="3">
-        <v>704000</v>
+        <v>514500</v>
       </c>
       <c r="H23" s="3">
-        <v>-1347000</v>
+        <v>621500</v>
       </c>
       <c r="I23" s="3">
-        <v>1413000</v>
+        <v>621500</v>
       </c>
       <c r="J23" s="3">
-        <v>1263000</v>
+        <v>402000</v>
       </c>
       <c r="K23" s="3">
         <v>2245000</v>
@@ -1663,25 +1663,25 @@
         <v>19</v>
       </c>
       <c r="D24" s="3">
-        <v>212000</v>
+        <v>162000</v>
       </c>
       <c r="E24" s="3">
-        <v>157000</v>
+        <v>162000</v>
       </c>
       <c r="F24" s="3">
-        <v>228000</v>
+        <v>132000</v>
       </c>
       <c r="G24" s="3">
-        <v>196000</v>
+        <v>132000</v>
       </c>
       <c r="H24" s="3">
-        <v>158000</v>
+        <v>148000</v>
       </c>
       <c r="I24" s="3">
-        <v>269000</v>
+        <v>148000</v>
       </c>
       <c r="J24" s="3">
-        <v>193000</v>
+        <v>148000</v>
       </c>
       <c r="K24" s="3">
         <v>311000</v>
@@ -1793,25 +1793,25 @@
         <v>21</v>
       </c>
       <c r="D26" s="3">
-        <v>182000</v>
+        <v>91000</v>
       </c>
       <c r="E26" s="3">
-        <v>765000</v>
+        <v>91000</v>
       </c>
       <c r="F26" s="3">
-        <v>947000</v>
+        <v>382500</v>
       </c>
       <c r="G26" s="3">
-        <v>508000</v>
+        <v>382500</v>
       </c>
       <c r="H26" s="3">
-        <v>-1505000</v>
+        <v>473500</v>
       </c>
       <c r="I26" s="3">
-        <v>1144000</v>
+        <v>473500</v>
       </c>
       <c r="J26" s="3">
-        <v>1070000</v>
+        <v>254000</v>
       </c>
       <c r="K26" s="3">
         <v>1934000</v>
@@ -1858,25 +1858,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>120000</v>
+        <v>60000</v>
       </c>
       <c r="E27" s="3">
-        <v>757000</v>
+        <v>60000</v>
       </c>
       <c r="F27" s="3">
-        <v>944000</v>
+        <v>378500</v>
       </c>
       <c r="G27" s="3">
-        <v>501000</v>
+        <v>378500</v>
       </c>
       <c r="H27" s="3">
-        <v>-1508000</v>
+        <v>472000</v>
       </c>
       <c r="I27" s="3">
-        <v>495000</v>
+        <v>472000</v>
       </c>
       <c r="J27" s="3">
-        <v>1697000</v>
+        <v>250500</v>
       </c>
       <c r="K27" s="3">
         <v>1946000</v>
@@ -1987,14 +1987,14 @@
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>8</v>
+      <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
+        <v>0</v>
+      </c>
+      <c r="F29" s="3">
+        <v>0</v>
       </c>
       <c r="G29" s="3">
         <v>0</v>
@@ -2003,10 +2003,10 @@
         <v>0</v>
       </c>
       <c r="I29" s="3">
-        <v>1473000</v>
+        <v>0</v>
       </c>
       <c r="J29" s="3">
-        <v>-5707000</v>
+        <v>0</v>
       </c>
       <c r="K29" s="3">
         <v>-340000</v>
@@ -2183,25 +2183,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>243000</v>
+        <v>-387500</v>
       </c>
       <c r="E32" s="3">
-        <v>18000</v>
+        <v>-387500</v>
       </c>
       <c r="F32" s="3">
-        <v>73000</v>
+        <v>-250000</v>
       </c>
       <c r="G32" s="3">
-        <v>-66000</v>
+        <v>-250000</v>
       </c>
       <c r="H32" s="3">
-        <v>-49000</v>
+        <v>-259500</v>
       </c>
       <c r="I32" s="3">
-        <v>-173000</v>
+        <v>-259500</v>
       </c>
       <c r="J32" s="3">
-        <v>-179000</v>
+        <v>-480000</v>
       </c>
       <c r="K32" s="3">
         <v>-384000</v>
@@ -2248,25 +2248,25 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>120000</v>
+        <v>60000</v>
       </c>
       <c r="E33" s="3">
-        <v>757000</v>
+        <v>60000</v>
       </c>
       <c r="F33" s="3">
-        <v>944000</v>
+        <v>378500</v>
       </c>
       <c r="G33" s="3">
-        <v>501000</v>
+        <v>378500</v>
       </c>
       <c r="H33" s="3">
-        <v>-1508000</v>
+        <v>472000</v>
       </c>
       <c r="I33" s="3">
-        <v>1968000</v>
+        <v>472000</v>
       </c>
       <c r="J33" s="3">
-        <v>-4010000</v>
+        <v>250500</v>
       </c>
       <c r="K33" s="3">
         <v>1606000</v>
@@ -2378,25 +2378,25 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>120000</v>
+        <v>60000</v>
       </c>
       <c r="E35" s="3">
-        <v>757000</v>
+        <v>60000</v>
       </c>
       <c r="F35" s="3">
-        <v>944000</v>
+        <v>378500</v>
       </c>
       <c r="G35" s="3">
-        <v>501000</v>
+        <v>378500</v>
       </c>
       <c r="H35" s="3">
-        <v>-1508000</v>
+        <v>472000</v>
       </c>
       <c r="I35" s="3">
-        <v>1968000</v>
+        <v>472000</v>
       </c>
       <c r="J35" s="3">
-        <v>-4010000</v>
+        <v>250500</v>
       </c>
       <c r="K35" s="3">
         <v>1606000</v>
@@ -2451,22 +2451,22 @@
         <v>45473</v>
       </c>
       <c r="E38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
+        <v>45199</v>
+      </c>
+      <c r="H38" s="2">
         <v>45107</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
+        <v>45016</v>
+      </c>
+      <c r="J38" s="2">
         <v>44926</v>
-      </c>
-      <c r="H38" s="2">
-        <v>44742</v>
-      </c>
-      <c r="I38" s="2">
-        <v>44561</v>
-      </c>
-      <c r="J38" s="2">
-        <v>44377</v>
       </c>
       <c r="K38" s="2">
         <v>44196</v>
@@ -2566,22 +2566,22 @@
         <v>5978000</v>
       </c>
       <c r="E41" s="3">
+        <v>5978000</v>
+      </c>
+      <c r="F41" s="3">
         <v>4751000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
+        <v>4751000</v>
+      </c>
+      <c r="H41" s="3">
         <v>5920000</v>
       </c>
-      <c r="G41" s="3">
-        <v>10279000</v>
-      </c>
-      <c r="H41" s="3">
-        <v>5647000</v>
-      </c>
       <c r="I41" s="3">
-        <v>6259000</v>
+        <v>5920000</v>
       </c>
       <c r="J41" s="3">
-        <v>5295000</v>
+        <v>5514000</v>
       </c>
       <c r="K41" s="3">
         <v>7431000</v>
@@ -2693,25 +2693,25 @@
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>2440000</v>
+        <v>3596000</v>
       </c>
       <c r="E43" s="3">
-        <v>1161000</v>
+        <v>3596000</v>
       </c>
       <c r="F43" s="3">
-        <v>1035000</v>
+        <v>2375000</v>
       </c>
       <c r="G43" s="3">
-        <v>2508000</v>
+        <v>2375000</v>
       </c>
       <c r="H43" s="3">
-        <v>1904000</v>
+        <v>2220000</v>
       </c>
       <c r="I43" s="3">
-        <v>1613000</v>
+        <v>2220000</v>
       </c>
       <c r="J43" s="3">
-        <v>1954000</v>
+        <v>2120000</v>
       </c>
       <c r="K43" s="3">
         <v>3171000</v>
@@ -2757,26 +2757,26 @@
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="D44" s="3">
-        <v>0</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3">
-        <v>0</v>
-      </c>
-      <c r="G44" s="3">
-        <v>0</v>
-      </c>
-      <c r="H44" s="3">
-        <v>0</v>
-      </c>
-      <c r="I44" s="3">
-        <v>0</v>
-      </c>
-      <c r="J44" s="3">
-        <v>0</v>
+      <c r="D44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K44" s="3">
         <v>0</v>
@@ -2823,25 +2823,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>0</v>
+        <v>4727000</v>
       </c>
       <c r="E45" s="3">
-        <v>0</v>
+        <v>4727000</v>
       </c>
       <c r="F45" s="3">
-        <v>0</v>
+        <v>5284000</v>
       </c>
       <c r="G45" s="3">
-        <v>0</v>
+        <v>5284000</v>
       </c>
       <c r="H45" s="3">
-        <v>0</v>
+        <v>3498000</v>
       </c>
       <c r="I45" s="3">
-        <v>0</v>
+        <v>3498000</v>
       </c>
       <c r="J45" s="3">
-        <v>0</v>
+        <v>3408000</v>
       </c>
       <c r="K45" s="3">
         <v>0</v>
@@ -2888,25 +2888,25 @@
         <v>39</v>
       </c>
       <c r="D46" s="3">
-        <v>0</v>
+        <v>14301000</v>
       </c>
       <c r="E46" s="3">
-        <v>0</v>
+        <v>14301000</v>
       </c>
       <c r="F46" s="3">
-        <v>0</v>
+        <v>12410000</v>
       </c>
       <c r="G46" s="3">
-        <v>0</v>
+        <v>12410000</v>
       </c>
       <c r="H46" s="3">
-        <v>0</v>
+        <v>11638000</v>
       </c>
       <c r="I46" s="3">
-        <v>0</v>
+        <v>11638000</v>
       </c>
       <c r="J46" s="3">
-        <v>0</v>
+        <v>11042000</v>
       </c>
       <c r="K46" s="3">
         <v>0</v>
@@ -2953,25 +2953,25 @@
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>156417000</v>
+        <v>154718000</v>
       </c>
       <c r="E47" s="3">
-        <v>157419000</v>
+        <v>154718000</v>
       </c>
       <c r="F47" s="3">
-        <v>149838000</v>
+        <v>155627000</v>
       </c>
       <c r="G47" s="3">
-        <v>179110000</v>
+        <v>155627000</v>
       </c>
       <c r="H47" s="3">
-        <v>122176000</v>
+        <v>148072000</v>
       </c>
       <c r="I47" s="3">
-        <v>170201000</v>
+        <v>148072000</v>
       </c>
       <c r="J47" s="3">
-        <v>161057000</v>
+        <v>143229000</v>
       </c>
       <c r="K47" s="3">
         <v>400592000</v>
@@ -3018,25 +3018,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>393000</v>
+        <v>390000</v>
       </c>
       <c r="E48" s="3">
-        <v>413000</v>
+        <v>390000</v>
       </c>
       <c r="F48" s="3">
-        <v>434000</v>
+        <v>374000</v>
       </c>
       <c r="G48" s="3">
-        <v>474000</v>
+        <v>374000</v>
       </c>
       <c r="H48" s="3">
-        <v>440000</v>
+        <v>396000</v>
       </c>
       <c r="I48" s="3">
-        <v>516000</v>
+        <v>396000</v>
       </c>
       <c r="J48" s="3">
-        <v>564000</v>
+        <v>437000</v>
       </c>
       <c r="K48" s="3">
         <v>916000</v>
@@ -3086,22 +3086,22 @@
         <v>4577000</v>
       </c>
       <c r="E49" s="3">
+        <v>4577000</v>
+      </c>
+      <c r="F49" s="3">
         <v>4882000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
+        <v>4882000</v>
+      </c>
+      <c r="H49" s="3">
         <v>4565000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
+        <v>4565000</v>
+      </c>
+      <c r="J49" s="3">
         <v>4774000</v>
-      </c>
-      <c r="H49" s="3">
-        <v>909000</v>
-      </c>
-      <c r="I49" s="3">
-        <v>956000</v>
-      </c>
-      <c r="J49" s="3">
-        <v>1000000</v>
       </c>
       <c r="K49" s="3">
         <v>1031000</v>
@@ -3278,25 +3278,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>446000</v>
+        <v>3000</v>
       </c>
       <c r="E52" s="3">
-        <v>156000</v>
+        <v>3000</v>
       </c>
       <c r="F52" s="3">
-        <v>168000</v>
+        <v>39000</v>
       </c>
       <c r="G52" s="3">
-        <v>140000</v>
+        <v>39000</v>
       </c>
       <c r="H52" s="3">
-        <v>378000</v>
+        <v>45000</v>
       </c>
       <c r="I52" s="3">
-        <v>266000</v>
+        <v>45000</v>
       </c>
       <c r="J52" s="3">
-        <v>336048000</v>
+        <v>37000</v>
       </c>
       <c r="K52" s="3">
         <v>4858000</v>
@@ -3411,22 +3411,22 @@
         <v>174687000</v>
       </c>
       <c r="E54" s="3">
+        <v>174687000</v>
+      </c>
+      <c r="F54" s="3">
         <v>174066000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
+        <v>174066000</v>
+      </c>
+      <c r="H54" s="3">
         <v>165458000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
+        <v>165458000</v>
+      </c>
+      <c r="J54" s="3">
         <v>160249000</v>
-      </c>
-      <c r="H54" s="3">
-        <v>166888000</v>
-      </c>
-      <c r="I54" s="3">
-        <v>199102000</v>
-      </c>
-      <c r="J54" s="3">
-        <v>525121000</v>
       </c>
       <c r="K54" s="3">
         <v>516097000</v>
@@ -3523,25 +3523,25 @@
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>0</v>
+        <v>1379000</v>
       </c>
       <c r="E57" s="3">
-        <v>0</v>
+        <v>1379000</v>
       </c>
       <c r="F57" s="3">
-        <v>0</v>
+        <v>1151000</v>
       </c>
       <c r="G57" s="3">
-        <v>0</v>
+        <v>1151000</v>
       </c>
       <c r="H57" s="3">
-        <v>0</v>
+        <v>950000</v>
       </c>
       <c r="I57" s="3">
-        <v>0</v>
+        <v>950000</v>
       </c>
       <c r="J57" s="3">
-        <v>0</v>
+        <v>1175000</v>
       </c>
       <c r="K57" s="3">
         <v>0</v>
@@ -3588,25 +3588,25 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>660000</v>
+        <v>1236000</v>
       </c>
       <c r="E58" s="3">
-        <v>699000</v>
+        <v>1236000</v>
       </c>
       <c r="F58" s="3">
-        <v>529000</v>
+        <v>1491000</v>
       </c>
       <c r="G58" s="3">
-        <v>501000</v>
+        <v>1491000</v>
       </c>
       <c r="H58" s="3">
-        <v>544000</v>
+        <v>1146000</v>
       </c>
       <c r="I58" s="3">
-        <v>500000</v>
+        <v>1146000</v>
       </c>
       <c r="J58" s="3">
-        <v>500000</v>
+        <v>1566000</v>
       </c>
       <c r="K58" s="3">
         <v>501000</v>
@@ -3653,25 +3653,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>150420000</v>
+        <v>3816000</v>
       </c>
       <c r="E59" s="3">
-        <v>149497000</v>
+        <v>3816000</v>
       </c>
       <c r="F59" s="3">
-        <v>141586000</v>
+        <v>3224000</v>
       </c>
       <c r="G59" s="3">
-        <v>269414000</v>
+        <v>3224000</v>
       </c>
       <c r="H59" s="3">
-        <v>141801000</v>
+        <v>3397000</v>
       </c>
       <c r="I59" s="3">
-        <v>171008000</v>
+        <v>3397000</v>
       </c>
       <c r="J59" s="3">
-        <v>165465000</v>
+        <v>5402000</v>
       </c>
       <c r="K59" s="3">
         <v>477515000</v>
@@ -3718,25 +3718,25 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>0</v>
+        <v>9639000</v>
       </c>
       <c r="E60" s="3">
-        <v>0</v>
+        <v>9639000</v>
       </c>
       <c r="F60" s="3">
-        <v>0</v>
+        <v>6145000</v>
       </c>
       <c r="G60" s="3">
-        <v>0</v>
+        <v>6145000</v>
       </c>
       <c r="H60" s="3">
-        <v>0</v>
+        <v>7571000</v>
       </c>
       <c r="I60" s="3">
-        <v>0</v>
+        <v>7571000</v>
       </c>
       <c r="J60" s="3">
-        <v>0</v>
+        <v>8402000</v>
       </c>
       <c r="K60" s="3">
         <v>0</v>
@@ -3786,22 +3786,22 @@
         <v>4231000</v>
       </c>
       <c r="E61" s="3">
-        <v>4175000</v>
+        <v>4231000</v>
       </c>
       <c r="F61" s="3">
+        <v>4099000</v>
+      </c>
+      <c r="G61" s="3">
+        <v>4099000</v>
+      </c>
+      <c r="H61" s="3">
         <v>4222000</v>
       </c>
-      <c r="G61" s="3">
-        <v>4575000</v>
-      </c>
-      <c r="H61" s="3">
-        <v>4576000</v>
-      </c>
       <c r="I61" s="3">
-        <v>6488000</v>
+        <v>4222000</v>
       </c>
       <c r="J61" s="3">
-        <v>6799000</v>
+        <v>4092000</v>
       </c>
       <c r="K61" s="3">
         <v>8576000</v>
@@ -3848,25 +3848,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>1577000</v>
+        <v>142242000</v>
       </c>
       <c r="E62" s="3">
-        <v>1250000</v>
+        <v>142242000</v>
       </c>
       <c r="F62" s="3">
-        <v>1214000</v>
+        <v>144589000</v>
       </c>
       <c r="G62" s="3">
-        <v>1139000</v>
+        <v>144589000</v>
       </c>
       <c r="H62" s="3">
-        <v>2699000</v>
+        <v>135140000</v>
       </c>
       <c r="I62" s="3">
-        <v>2862000</v>
+        <v>135140000</v>
       </c>
       <c r="J62" s="3">
-        <v>335495000</v>
+        <v>129718000</v>
       </c>
       <c r="K62" s="3">
         <v>6075000</v>
@@ -4108,25 +4108,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>158516000</v>
+        <v>157451000</v>
       </c>
       <c r="E66" s="3">
-        <v>156243000</v>
+        <v>157451000</v>
       </c>
       <c r="F66" s="3">
-        <v>148299000</v>
+        <v>156083000</v>
       </c>
       <c r="G66" s="3">
-        <v>143518000</v>
+        <v>156083000</v>
       </c>
       <c r="H66" s="3">
-        <v>150779000</v>
+        <v>148147000</v>
       </c>
       <c r="I66" s="3">
-        <v>182014000</v>
+        <v>148147000</v>
       </c>
       <c r="J66" s="3">
-        <v>509408000</v>
+        <v>143351000</v>
       </c>
       <c r="K66" s="3">
         <v>495219000</v>
@@ -4457,26 +4457,26 @@
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D72" s="3" t="s">
-        <v>8</v>
+      <c r="D72" s="3">
+        <v>10650000</v>
       </c>
       <c r="E72" s="3">
+        <v>10650000</v>
+      </c>
+      <c r="F72" s="3">
         <v>11928000</v>
       </c>
-      <c r="F72" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="G72" s="3">
-        <v>10810000</v>
+        <v>11928000</v>
       </c>
       <c r="H72" s="3">
-        <v>9997000</v>
+        <v>11325000</v>
       </c>
       <c r="I72" s="3">
-        <v>10216000</v>
+        <v>11325000</v>
       </c>
       <c r="J72" s="3">
-        <v>10180000</v>
+        <v>10653000</v>
       </c>
       <c r="K72" s="3">
         <v>14424000</v>
@@ -4721,22 +4721,22 @@
         <v>16171000</v>
       </c>
       <c r="E76" s="3">
+        <v>16171000</v>
+      </c>
+      <c r="F76" s="3">
         <v>17823000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
+        <v>17823000</v>
+      </c>
+      <c r="H76" s="3">
         <v>17159000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
+        <v>17159000</v>
+      </c>
+      <c r="J76" s="3">
         <v>16731000</v>
-      </c>
-      <c r="H76" s="3">
-        <v>16109000</v>
-      </c>
-      <c r="I76" s="3">
-        <v>17088000</v>
-      </c>
-      <c r="J76" s="3">
-        <v>15713000</v>
       </c>
       <c r="K76" s="3">
         <v>20878000</v>
@@ -4856,22 +4856,22 @@
         <v>45473</v>
       </c>
       <c r="E80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
+        <v>45199</v>
+      </c>
+      <c r="H80" s="2">
         <v>45107</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
+        <v>45016</v>
+      </c>
+      <c r="J80" s="2">
         <v>44926</v>
-      </c>
-      <c r="H80" s="2">
-        <v>44742</v>
-      </c>
-      <c r="I80" s="2">
-        <v>44561</v>
-      </c>
-      <c r="J80" s="2">
-        <v>44377</v>
       </c>
       <c r="K80" s="2">
         <v>44196</v>
@@ -4918,25 +4918,25 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>120000</v>
+        <v>60000</v>
       </c>
       <c r="E81" s="3">
-        <v>757000</v>
+        <v>60000</v>
       </c>
       <c r="F81" s="3">
-        <v>944000</v>
+        <v>378500</v>
       </c>
       <c r="G81" s="3">
-        <v>501000</v>
+        <v>378500</v>
       </c>
       <c r="H81" s="3">
-        <v>-1508000</v>
+        <v>472000</v>
       </c>
       <c r="I81" s="3">
-        <v>1968000</v>
+        <v>472000</v>
       </c>
       <c r="J81" s="3">
-        <v>-4010000</v>
+        <v>250500</v>
       </c>
       <c r="K81" s="3">
         <v>1606000</v>
@@ -5007,26 +5007,26 @@
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3">
-        <v>0</v>
-      </c>
-      <c r="E83" s="3">
-        <v>0</v>
+      <c r="D83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E83" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F83" s="3">
-        <v>0</v>
+        <v>72500</v>
       </c>
       <c r="G83" s="3">
-        <v>0</v>
-      </c>
-      <c r="H83" s="3">
-        <v>0</v>
-      </c>
-      <c r="I83" s="3">
-        <v>0</v>
+        <v>72500</v>
+      </c>
+      <c r="H83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="J83" s="3">
-        <v>0</v>
+        <v>42000</v>
       </c>
       <c r="K83" s="3">
         <v>0</v>
@@ -5398,25 +5398,25 @@
         <v>78</v>
       </c>
       <c r="D89" s="3">
-        <v>2173000</v>
+        <v>1086500</v>
       </c>
       <c r="E89" s="3">
-        <v>-435000</v>
+        <v>1086500</v>
       </c>
       <c r="F89" s="3">
-        <v>1267000</v>
+        <v>-217500</v>
       </c>
       <c r="G89" s="3">
-        <v>-638000</v>
+        <v>-217500</v>
       </c>
       <c r="H89" s="3">
-        <v>1716000</v>
+        <v>633500</v>
       </c>
       <c r="I89" s="3">
-        <v>-2111000</v>
+        <v>633500</v>
       </c>
       <c r="J89" s="3">
-        <v>768000</v>
+        <v>-319000</v>
       </c>
       <c r="K89" s="3">
         <v>325000</v>
@@ -5488,25 +5488,25 @@
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-27000</v>
+        <v>-13500</v>
       </c>
       <c r="E91" s="3">
-        <v>-26000</v>
+        <v>-13500</v>
       </c>
       <c r="F91" s="3">
-        <v>-18000</v>
+        <v>-13000</v>
       </c>
       <c r="G91" s="3">
-        <v>-20000</v>
+        <v>-13000</v>
       </c>
       <c r="H91" s="3">
-        <v>-14000</v>
+        <v>-9000</v>
       </c>
       <c r="I91" s="3">
-        <v>-17000</v>
+        <v>-9000</v>
       </c>
       <c r="J91" s="3">
-        <v>-19000</v>
+        <v>-10000</v>
       </c>
       <c r="K91" s="3">
         <v>-14000</v>
@@ -5683,25 +5683,25 @@
         <v>83</v>
       </c>
       <c r="D94" s="3">
-        <v>-270000</v>
+        <v>-135000</v>
       </c>
       <c r="E94" s="3">
-        <v>-418000</v>
+        <v>-135000</v>
       </c>
       <c r="F94" s="3">
-        <v>58000</v>
+        <v>-209000</v>
       </c>
       <c r="G94" s="3">
-        <v>25000</v>
+        <v>-209000</v>
       </c>
       <c r="H94" s="3">
-        <v>-64000</v>
+        <v>29000</v>
       </c>
       <c r="I94" s="3">
-        <v>66000</v>
+        <v>29000</v>
       </c>
       <c r="J94" s="3">
-        <v>-792000</v>
+        <v>12500</v>
       </c>
       <c r="K94" s="3">
         <v>-417000</v>
@@ -5773,25 +5773,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-390000</v>
+        <v>195000</v>
       </c>
       <c r="E96" s="3">
-        <v>-172000</v>
+        <v>195000</v>
       </c>
       <c r="F96" s="3">
-        <v>-361000</v>
+        <v>86000</v>
       </c>
       <c r="G96" s="3">
-        <v>-154000</v>
+        <v>86000</v>
       </c>
       <c r="H96" s="3">
-        <v>-320000</v>
+        <v>180500</v>
       </c>
       <c r="I96" s="3">
-        <v>-138000</v>
+        <v>180500</v>
       </c>
       <c r="J96" s="3">
-        <v>-283000</v>
+        <v>77000</v>
       </c>
       <c r="K96" s="3">
         <v>-140000</v>
@@ -6033,25 +6033,25 @@
         <v>89</v>
       </c>
       <c r="D100" s="3">
-        <v>-571000</v>
+        <v>-285500</v>
       </c>
       <c r="E100" s="3">
-        <v>-331000</v>
+        <v>-285500</v>
       </c>
       <c r="F100" s="3">
-        <v>-879000</v>
+        <v>-165500</v>
       </c>
       <c r="G100" s="3">
-        <v>-293000</v>
+        <v>-165500</v>
       </c>
       <c r="H100" s="3">
-        <v>-2227000</v>
+        <v>-439500</v>
       </c>
       <c r="I100" s="3">
-        <v>1760000</v>
+        <v>-439500</v>
       </c>
       <c r="J100" s="3">
-        <v>-495000</v>
+        <v>-146500</v>
       </c>
       <c r="K100" s="3">
         <v>67000</v>
@@ -6098,25 +6098,25 @@
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>-105000</v>
+        <v>-20000</v>
       </c>
       <c r="E101" s="3">
-        <v>15000</v>
+        <v>-20000</v>
       </c>
       <c r="F101" s="3">
-        <v>-40000</v>
+        <v>2500</v>
       </c>
       <c r="G101" s="3">
-        <v>5000</v>
+        <v>2500</v>
       </c>
       <c r="H101" s="3">
-        <v>-180000</v>
+        <v>-90000</v>
       </c>
       <c r="I101" s="3">
-        <v>-1000</v>
+        <v>-90000</v>
       </c>
       <c r="J101" s="3">
-        <v>-43000</v>
+        <v>-500</v>
       </c>
       <c r="K101" s="3">
         <v>129000</v>
@@ -6163,25 +6163,25 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>1227000</v>
+        <v>613500</v>
       </c>
       <c r="E102" s="3">
-        <v>-1169000</v>
+        <v>613500</v>
       </c>
       <c r="F102" s="3">
-        <v>406000</v>
+        <v>-584500</v>
       </c>
       <c r="G102" s="3">
-        <v>-901000</v>
+        <v>-584500</v>
       </c>
       <c r="H102" s="3">
-        <v>-755000</v>
+        <v>203000</v>
       </c>
       <c r="I102" s="3">
-        <v>-286000</v>
+        <v>203000</v>
       </c>
       <c r="J102" s="3">
-        <v>-562000</v>
+        <v>-450500</v>
       </c>
       <c r="K102" s="3">
         <v>-366000</v>

--- a/AAII_Financials/Quarterly/PUK_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PUK_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="164" uniqueCount="92">
   <si>
     <t>PUK</t>
   </si>
@@ -656,287 +656,311 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:W102"/>
+  <dimension ref="A5:Y102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="23" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="25" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45565</v>
+      </c>
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45107</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45016</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>44196</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>44012</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>43830</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>43646</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>43465</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>43281</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>43100</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>42916</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>42735</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>42551</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>42369</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>42185</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>42004</v>
       </c>
     </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>3373500</v>
+      </c>
+      <c r="E8" s="3">
+        <v>3373500</v>
+      </c>
+      <c r="F8" s="3">
         <v>2662500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>2662500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="H8" s="3">
         <v>2809500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="I8" s="3">
         <v>2809500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="J8" s="3">
         <v>2709500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>2709500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>2797500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>42311000</v>
       </c>
-      <c r="L8" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O8" s="3">
         <v>41197000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>52539000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>35845000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="R8" s="3">
         <v>16019000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>43466000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>42924000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>36301000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>45947800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>20902900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>33287100</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>38844000</v>
       </c>
     </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>2087500</v>
+      </c>
+      <c r="E9" s="3">
+        <v>2087500</v>
+      </c>
+      <c r="F9" s="3">
         <v>1945000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>1945000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>1856000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>1856000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>1786000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>1786000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>1735500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>647000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>1433000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>2068000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>2109000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>6103000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>3186000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>1792000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>1920000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>1987000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>2197800</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>2210800</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>2080500</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>4498200</v>
       </c>
     </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1286000</v>
+      </c>
+      <c r="E10" s="3">
+        <v>1286000</v>
+      </c>
+      <c r="F10" s="3">
         <v>717500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>717500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="H10" s="3">
         <v>953500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="I10" s="3">
         <v>953500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="J10" s="3">
         <v>923500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>923500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>1062000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>41664000</v>
       </c>
-      <c r="L10" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O10" s="3">
         <v>39129000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>50430000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>29742000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="R10" s="3">
         <v>12833000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>41674000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>41004000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>34314000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>43750000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>18692100</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>31206600</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>34345800</v>
       </c>
     </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -960,8 +984,10 @@
       <c r="U11" s="3"/>
       <c r="V11" s="3"/>
       <c r="W11" s="3"/>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X11" s="3"/>
+      <c r="Y11" s="3"/>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1025,8 +1051,14 @@
       <c r="W12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1090,23 +1122,29 @@
       <c r="W13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E14" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F14" s="3">
         <v>34500</v>
       </c>
-      <c r="E14" s="3">
+      <c r="G14" s="3">
         <v>34500</v>
       </c>
-      <c r="F14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="H14" s="3" t="s">
         <v>8</v>
       </c>
@@ -1116,103 +1154,109 @@
       <c r="J14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K14" s="3">
+      <c r="K14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M14" s="3">
         <v>30000</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
-      </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
+        <v>0</v>
+      </c>
+      <c r="O14" s="3">
         <v>159000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="P14" s="3">
         <v>-17000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="Q14" s="3">
         <v>182000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="R14" s="3">
         <v>570000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="S14" s="3">
         <v>-162000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="T14" s="3">
         <v>-66000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="U14" s="3">
         <v>238000</v>
       </c>
-      <c r="T14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="U14" s="3">
-        <v>0</v>
-      </c>
-      <c r="V14" s="3">
-        <v>0</v>
+      <c r="V14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="W14" s="3">
+        <v>0</v>
+      </c>
+      <c r="X14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="3">
         <v>2600</v>
       </c>
     </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>92000</v>
+      </c>
+      <c r="E15" s="3">
+        <v>92000</v>
+      </c>
+      <c r="F15" s="3">
         <v>102500</v>
       </c>
-      <c r="E15" s="3">
+      <c r="G15" s="3">
         <v>102500</v>
       </c>
-      <c r="F15" s="3">
+      <c r="H15" s="3">
         <v>106500</v>
       </c>
-      <c r="G15" s="3">
+      <c r="I15" s="3">
         <v>106500</v>
       </c>
-      <c r="H15" s="3">
+      <c r="J15" s="3">
         <v>108000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="K15" s="3">
         <v>108000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="L15" s="3">
         <v>169000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="M15" s="3">
         <v>77000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="N15" s="3">
         <v>109000</v>
       </c>
-      <c r="M15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P15" s="3">
         <v>107000</v>
       </c>
-      <c r="O15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P15" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="Q15" s="3" t="s">
         <v>8</v>
       </c>
       <c r="R15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S15" s="3">
-        <v>0</v>
+      <c r="S15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="T15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U15" s="3" t="s">
-        <v>8</v>
+      <c r="U15" s="3">
+        <v>0</v>
       </c>
       <c r="V15" s="3" t="s">
         <v>8</v>
@@ -1220,8 +1264,14 @@
       <c r="W15" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="X15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y15" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1242,138 +1292,152 @@
       <c r="U16" s="3"/>
       <c r="V16" s="3"/>
       <c r="W16" s="3"/>
-    </row>
-    <row r="17" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X16" s="3"/>
+      <c r="Y16" s="3"/>
+    </row>
+    <row r="17" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2087500</v>
+      </c>
+      <c r="E17" s="3">
+        <v>2087500</v>
+      </c>
+      <c r="F17" s="3">
         <v>1945000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>1945000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>1856000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>1856000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>1786000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>1786000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>1735500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>40297000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>-6757000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>40471000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>51224000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>32167000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>14313000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>41957000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>41014000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>34595000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>44982000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>19189000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>30714100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>37257300</v>
       </c>
     </row>
-    <row r="18" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>1286000</v>
+      </c>
+      <c r="E18" s="3">
+        <v>1286000</v>
+      </c>
+      <c r="F18" s="3">
         <v>717500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>717500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="H18" s="3">
         <v>953500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="I18" s="3">
         <v>953500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="J18" s="3">
         <v>923500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>923500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>1062000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>2014000</v>
       </c>
-      <c r="L18" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O18" s="3">
         <v>726000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>1315000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>3678000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="R18" s="3">
         <v>1706000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>1509000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>1910000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>1706000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>965700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>1713900</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>2573000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>1586700</v>
       </c>
     </row>
-    <row r="19" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1397,333 +1461,365 @@
       <c r="U19" s="3"/>
       <c r="V19" s="3"/>
       <c r="W19" s="3"/>
-    </row>
-    <row r="20" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X19" s="3"/>
+      <c r="Y19" s="3"/>
+    </row>
+    <row r="20" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-124500</v>
+      </c>
+      <c r="E20" s="3">
+        <v>-124500</v>
+      </c>
+      <c r="F20" s="3">
         <v>387500</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>387500</v>
       </c>
-      <c r="F20" s="3">
+      <c r="H20" s="3">
         <v>250000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="I20" s="3">
         <v>250000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="J20" s="3">
         <v>259500</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>259500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>480000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>384000</v>
       </c>
-      <c r="L20" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O20" s="3">
         <v>260000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>137000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>319000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="R20" s="3">
         <v>82000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>182000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>120000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>96000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>111200</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>151300</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>100100</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>205400</v>
       </c>
     </row>
-    <row r="21" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>1502500</v>
+      </c>
+      <c r="E21" s="3">
+        <v>1502500</v>
+      </c>
+      <c r="F21" s="3">
         <v>432500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>432500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="H21" s="3">
         <v>810000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="I21" s="3">
         <v>810000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="J21" s="3">
         <v>772000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>772000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>751000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>2366000</v>
       </c>
-      <c r="L21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O21" s="3">
         <v>999000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>1559000</v>
       </c>
-      <c r="O21" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R21" s="3">
         <v>1822000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>1687000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>2090000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="U21" s="3">
         <v>1811000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>1173900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>1889900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>2745500</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>1792200</v>
       </c>
     </row>
-    <row r="22" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>43000</v>
+      </c>
+      <c r="E22" s="3">
+        <v>43000</v>
+      </c>
+      <c r="F22" s="3">
         <v>42500</v>
       </c>
-      <c r="E22" s="3">
+      <c r="G22" s="3">
         <v>42500</v>
       </c>
-      <c r="F22" s="3">
+      <c r="H22" s="3">
         <v>189000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="I22" s="3">
         <v>189000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="J22" s="3">
         <v>42500</v>
       </c>
-      <c r="I22" s="3">
+      <c r="K22" s="3">
         <v>42500</v>
       </c>
-      <c r="J22" s="3">
+      <c r="L22" s="3">
         <v>180000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="M22" s="3">
         <v>153000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="N22" s="3">
         <v>163000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="O22" s="3">
         <v>223000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="P22" s="3">
         <v>293000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="Q22" s="3">
         <v>547000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="R22" s="3">
         <v>189000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="S22" s="3">
         <v>209000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="T22" s="3">
         <v>216000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="U22" s="3">
         <v>191000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="V22" s="3">
         <v>218500</v>
       </c>
-      <c r="U22" s="3">
+      <c r="W22" s="3">
         <v>213900</v>
       </c>
-      <c r="V22" s="3">
+      <c r="X22" s="3">
         <v>194900</v>
       </c>
-      <c r="W22" s="3">
+      <c r="Y22" s="3">
         <v>225200</v>
       </c>
     </row>
-    <row r="23" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>1366500</v>
+      </c>
+      <c r="E23" s="3">
+        <v>1366500</v>
+      </c>
+      <c r="F23" s="3">
         <v>253000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>253000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>514500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>514500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>621500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>621500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>402000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>2245000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>663000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>763000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>1159000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>3450000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>1599000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>1482000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>1814000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>1611000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>858400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>1651300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>2478200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>1567000</v>
       </c>
     </row>
-    <row r="24" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>250000</v>
+      </c>
+      <c r="E24" s="3">
+        <v>250000</v>
+      </c>
+      <c r="F24" s="3">
         <v>162000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>162000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>132000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>132000</v>
-      </c>
-      <c r="H24" s="3">
-        <v>148000</v>
-      </c>
-      <c r="I24" s="3">
-        <v>148000</v>
       </c>
       <c r="J24" s="3">
         <v>148000</v>
       </c>
       <c r="K24" s="3">
+        <v>148000</v>
+      </c>
+      <c r="L24" s="3">
+        <v>148000</v>
+      </c>
+      <c r="M24" s="3">
         <v>311000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="N24" s="3">
         <v>129000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="O24" s="3">
         <v>-32000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="P24" s="3">
         <v>1000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="Q24" s="3">
         <v>569000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>326000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>152000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>309000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>377000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>-29700</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>163000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>584700</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>156700</v>
       </c>
     </row>
-    <row r="25" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1787,138 +1883,156 @@
       <c r="W25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>1116500</v>
+      </c>
+      <c r="E26" s="3">
+        <v>1116500</v>
+      </c>
+      <c r="F26" s="3">
         <v>91000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>91000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>382500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>382500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>473500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>473500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>254000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>1934000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>534000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>795000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>1158000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>2881000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>1273000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>1330000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>1505000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>1234000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>888200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>1488200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>1893500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>1410300</v>
       </c>
     </row>
-    <row r="27" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>1082500</v>
+      </c>
+      <c r="E27" s="3">
+        <v>1082500</v>
+      </c>
+      <c r="F27" s="3">
         <v>60000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>60000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>378500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>378500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>472000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>472000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>250500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>1946000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>512000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>792000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>1152000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>2877000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>1272000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>1329000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>1505000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>1234000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>888200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>1488200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>1893500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>1410300</v>
       </c>
     </row>
-    <row r="28" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1982,8 +2096,14 @@
       <c r="W28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2009,32 +2129,32 @@
         <v>0</v>
       </c>
       <c r="K29" s="3">
+        <v>0</v>
+      </c>
+      <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3">
         <v>-340000</v>
       </c>
-      <c r="L29" s="3">
-        <v>0</v>
-      </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
+        <v>0</v>
+      </c>
+      <c r="O29" s="3">
         <v>-1996000</v>
       </c>
-      <c r="N29" s="3">
+      <c r="P29" s="3">
         <v>1480000</v>
       </c>
-      <c r="O29" s="3">
+      <c r="Q29" s="3">
         <v>1142000</v>
       </c>
-      <c r="P29" s="3">
+      <c r="R29" s="3">
         <v>83000</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="S29" s="3">
         <v>-445000</v>
       </c>
-      <c r="R29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="S29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="T29" s="3" t="s">
         <v>8</v>
       </c>
@@ -2047,8 +2167,14 @@
       <c r="W29" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="30" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y29" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2112,8 +2238,14 @@
       <c r="W30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2177,138 +2309,156 @@
       <c r="W31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>124500</v>
+      </c>
+      <c r="E32" s="3">
+        <v>124500</v>
+      </c>
+      <c r="F32" s="3">
         <v>-387500</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>-387500</v>
       </c>
-      <c r="F32" s="3">
+      <c r="H32" s="3">
         <v>-250000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="I32" s="3">
         <v>-250000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="J32" s="3">
         <v>-259500</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>-259500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>-480000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>-384000</v>
       </c>
-      <c r="L32" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O32" s="3">
         <v>-260000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>-137000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>-319000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="R32" s="3">
         <v>-82000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>-182000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>-120000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>-96000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>-111200</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>-151300</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>-100100</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>-205400</v>
       </c>
     </row>
-    <row r="33" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1082500</v>
+      </c>
+      <c r="E33" s="3">
+        <v>1082500</v>
+      </c>
+      <c r="F33" s="3">
         <v>60000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>60000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>378500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>378500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>472000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>472000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>250500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>1606000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>512000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>-1204000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>2632000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>4019000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>1355000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>884000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>1505000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>1234000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>888200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>1488200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>1893500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>1410300</v>
       </c>
     </row>
-    <row r="34" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2372,143 +2522,161 @@
       <c r="W34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1082500</v>
+      </c>
+      <c r="E35" s="3">
+        <v>1082500</v>
+      </c>
+      <c r="F35" s="3">
         <v>60000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>60000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>378500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>378500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>472000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>472000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>250500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>1606000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>512000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>-1204000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>2632000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>4019000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>1355000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>884000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>1505000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>1234000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>888200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>1488200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>1893500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>1410300</v>
       </c>
     </row>
-    <row r="37" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45565</v>
+      </c>
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45107</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45016</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>44196</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>44012</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>43830</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>43646</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>43465</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>43281</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>43100</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>42916</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>42735</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>42551</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>42369</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>42185</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>42004</v>
       </c>
     </row>
-    <row r="39" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2532,8 +2700,10 @@
       <c r="U39" s="3"/>
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
-    </row>
-    <row r="40" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X39" s="3"/>
+      <c r="Y39" s="3"/>
+    </row>
+    <row r="40" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2557,73 +2727,81 @@
       <c r="U40" s="3"/>
       <c r="V40" s="3"/>
       <c r="W40" s="3"/>
-    </row>
-    <row r="41" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X40" s="3"/>
+      <c r="Y40" s="3"/>
+    </row>
+    <row r="41" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>5772000</v>
+      </c>
+      <c r="E41" s="3">
+        <v>5772000</v>
+      </c>
+      <c r="F41" s="3">
         <v>5978000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>5978000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="H41" s="3">
         <v>4751000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="I41" s="3">
         <v>4751000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="J41" s="3">
         <v>5920000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>5920000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>5514000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>7431000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>7785000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>6609000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>6119000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>27051000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>8312000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>20400000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>19024000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>9843000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>11027700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>9676700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>10926700</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>8439300</v>
       </c>
     </row>
-    <row r="42" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2687,73 +2865,85 @@
       <c r="W42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2686000</v>
+      </c>
+      <c r="E43" s="3">
+        <v>2686000</v>
+      </c>
+      <c r="F43" s="3">
         <v>3596000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>3596000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>2375000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>2375000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>2220000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>2220000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>2120000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>3171000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>2729000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>2054000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>2159000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>7990000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>3120000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>5681000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>6610000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>2872000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>4531300</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>2549900</v>
       </c>
-      <c r="V43" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="W43" s="3" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="44" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X43" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y43" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -2778,11 +2968,11 @@
       <c r="J44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K44" s="3">
-        <v>0</v>
-      </c>
-      <c r="L44" s="3">
-        <v>0</v>
+      <c r="K44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M44" s="3">
         <v>0</v>
@@ -2817,38 +3007,44 @@
       <c r="W44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X44" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>4983000</v>
+      </c>
+      <c r="E45" s="3">
+        <v>4983000</v>
+      </c>
+      <c r="F45" s="3">
         <v>4727000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>4727000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>5284000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>5284000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>3498000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>3498000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>3408000</v>
       </c>
-      <c r="K45" s="3">
-        <v>0</v>
-      </c>
-      <c r="L45" s="3">
-        <v>0</v>
-      </c>
       <c r="M45" s="3">
         <v>0</v>
       </c>
@@ -2882,38 +3078,44 @@
       <c r="W45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X45" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>13441000</v>
+      </c>
+      <c r="E46" s="3">
+        <v>13441000</v>
+      </c>
+      <c r="F46" s="3">
         <v>14301000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>14301000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>12410000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>12410000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>11638000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>11638000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>11042000</v>
       </c>
-      <c r="K46" s="3">
-        <v>0</v>
-      </c>
-      <c r="L46" s="3">
-        <v>0</v>
-      </c>
       <c r="M46" s="3">
         <v>0</v>
       </c>
@@ -2947,203 +3149,227 @@
       <c r="W46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X46" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>162684000</v>
+      </c>
+      <c r="E47" s="3">
+        <v>162684000</v>
+      </c>
+      <c r="F47" s="3">
         <v>154718000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>154718000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>155627000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>155627000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>148072000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>148072000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>143229000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>400592000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>377884000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>379715000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>639141000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>913733000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>404637000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>802481000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="T47" s="3">
         <v>796888000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="U47" s="3">
         <v>388381000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="V47" s="3">
         <v>476271200</v>
       </c>
-      <c r="U47" s="3">
+      <c r="W47" s="3">
         <v>424114700</v>
       </c>
-      <c r="V47" s="3">
+      <c r="X47" s="3">
         <v>434640800</v>
       </c>
-      <c r="W47" s="3">
+      <c r="Y47" s="3">
         <v>427702600</v>
       </c>
     </row>
-    <row r="48" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>417000</v>
+      </c>
+      <c r="E48" s="3">
+        <v>417000</v>
+      </c>
+      <c r="F48" s="3">
         <v>390000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>390000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>374000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>374000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>396000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>396000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>437000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>916000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>987000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>1090000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>1798000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>24624000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>18556000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>33101000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>30513000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>15389000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>19591200</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>19067700</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>18755000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>18095300</v>
       </c>
     </row>
-    <row r="49" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>4672000</v>
+      </c>
+      <c r="E49" s="3">
+        <v>4672000</v>
+      </c>
+      <c r="F49" s="3">
         <v>4577000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>4577000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>4882000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>4882000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>4565000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>4565000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>4774000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>1031000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>1008000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>1036000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>723000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>4193000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>1769000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>1627000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>1615000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>1680000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>2226200</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>2214700</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>2166100</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>2171400</v>
       </c>
     </row>
-    <row r="50" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3207,8 +3433,14 @@
       <c r="W50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3272,8 +3504,14 @@
       <c r="W51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3284,61 +3522,67 @@
         <v>3000</v>
       </c>
       <c r="F52" s="3">
+        <v>3000</v>
+      </c>
+      <c r="G52" s="3">
+        <v>3000</v>
+      </c>
+      <c r="H52" s="3">
         <v>39000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="I52" s="3">
         <v>39000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="J52" s="3">
         <v>45000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="K52" s="3">
         <v>45000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="L52" s="3">
         <v>37000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>4858000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>4259000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>4075000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>284138000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>29949000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>14459000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>5330000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>8276000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>6027000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>4914000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>3678200</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>3713300</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>4726000</v>
       </c>
     </row>
-    <row r="53" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3402,73 +3646,85 @@
       <c r="W53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>181876000</v>
+      </c>
+      <c r="E54" s="3">
+        <v>181876000</v>
+      </c>
+      <c r="F54" s="3">
         <v>174687000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>174687000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>174066000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>174066000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>165458000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>165458000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>160249000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>516097000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>463165000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>454214000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>705945000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>647810000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>501170000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>493941000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>481130000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>470498000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>567962500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>504748400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>497616300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>486164100</v>
       </c>
     </row>
-    <row r="55" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -3492,8 +3748,10 @@
       <c r="U55" s="3"/>
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
-    </row>
-    <row r="56" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X55" s="3"/>
+      <c r="Y55" s="3"/>
+    </row>
+    <row r="56" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -3517,38 +3775,40 @@
       <c r="U56" s="3"/>
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
-    </row>
-    <row r="57" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X56" s="3"/>
+      <c r="Y56" s="3"/>
+    </row>
+    <row r="57" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>536000</v>
+      </c>
+      <c r="E57" s="3">
+        <v>536000</v>
+      </c>
+      <c r="F57" s="3">
         <v>1379000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>1379000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>1151000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>1151000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>950000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>950000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>1175000</v>
       </c>
-      <c r="K57" s="3">
-        <v>0</v>
-      </c>
-      <c r="L57" s="3">
-        <v>0</v>
-      </c>
       <c r="M57" s="3">
         <v>0</v>
       </c>
@@ -3582,64 +3842,70 @@
       <c r="W57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X57" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>799000</v>
+      </c>
+      <c r="E58" s="3">
+        <v>799000</v>
+      </c>
+      <c r="F58" s="3">
         <v>1236000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>1236000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>1491000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>1491000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>1146000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>1146000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>1566000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>501000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>506000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>549000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>841000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>716000</v>
       </c>
-      <c r="P58" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q58" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R58" s="3" t="s">
         <v>8</v>
       </c>
       <c r="S58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T58" s="3">
-        <v>0</v>
-      </c>
-      <c r="U58" s="3">
-        <v>0</v>
+      <c r="T58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="U58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="V58" s="3">
         <v>0</v>
@@ -3647,103 +3913,115 @@
       <c r="W58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X58" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>4778000</v>
+      </c>
+      <c r="E59" s="3">
+        <v>4778000</v>
+      </c>
+      <c r="F59" s="3">
         <v>3816000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>3816000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>3224000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>3224000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>3397000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>3397000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>5402000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>477515000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>429139000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>419599000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>393980000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>830364000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>453226000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>816205000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>866408000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>369166000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>507721400</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>399974500</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>448806800</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>360479200</v>
       </c>
     </row>
-    <row r="60" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>8961000</v>
+      </c>
+      <c r="E60" s="3">
+        <v>8961000</v>
+      </c>
+      <c r="F60" s="3">
         <v>9639000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>9639000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>6145000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>6145000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>7571000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>7571000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>8402000</v>
       </c>
-      <c r="K60" s="3">
-        <v>0</v>
-      </c>
-      <c r="L60" s="3">
-        <v>0</v>
-      </c>
       <c r="M60" s="3">
         <v>0</v>
       </c>
@@ -3777,138 +4055,156 @@
       <c r="W60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X60" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>4195000</v>
+      </c>
+      <c r="E61" s="3">
+        <v>4195000</v>
+      </c>
+      <c r="F61" s="3">
         <v>4231000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>4231000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>4099000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>4099000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>4222000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>4222000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>4092000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>8576000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>8223000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>7669000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>11004000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>15334000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>11570000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>11787000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>12046000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>10452000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>13166000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>10829700</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>11157200</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>10086600</v>
       </c>
     </row>
-    <row r="62" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>148532000</v>
+      </c>
+      <c r="E62" s="3">
+        <v>148532000</v>
+      </c>
+      <c r="F62" s="3">
         <v>142242000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>142242000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>144589000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>144589000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>135140000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>135140000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>129718000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>6075000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>5278000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>5237000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>277443000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>33150000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>16420000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>9392000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>11366000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>6761000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>6938500</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>5195100</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>5695100</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>5650300</v>
       </c>
     </row>
-    <row r="63" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3972,8 +4268,14 @@
       <c r="W63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4037,8 +4339,14 @@
       <c r="W64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4102,73 +4410,85 @@
       <c r="W65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>163202000</v>
+      </c>
+      <c r="E66" s="3">
+        <v>163202000</v>
+      </c>
+      <c r="F66" s="3">
         <v>157451000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>157451000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>156083000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>156083000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>148147000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>148147000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>143351000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>495219000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>444055000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>434737000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>680908000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>625842000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>485288000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>477854000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>465681000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>455832000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>549081000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>487851100</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>481677800</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>470611500</v>
       </c>
     </row>
-    <row r="67" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4192,8 +4512,10 @@
       <c r="U67" s="3"/>
       <c r="V67" s="3"/>
       <c r="W67" s="3"/>
-    </row>
-    <row r="68" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X67" s="3"/>
+      <c r="Y67" s="3"/>
+    </row>
+    <row r="68" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4257,8 +4579,14 @@
       <c r="W68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4322,8 +4650,14 @@
       <c r="W69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -4387,8 +4721,14 @@
       <c r="W70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -4452,73 +4792,85 @@
       <c r="W71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>11906000</v>
+      </c>
+      <c r="E72" s="3">
+        <v>11906000</v>
+      </c>
+      <c r="F72" s="3">
         <v>10650000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>10650000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>11928000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>11928000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>11325000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>11325000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>10653000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>14424000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>13420000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>13575000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>22597000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>21817000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>12954000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>12326000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>11700000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>10942000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>13160800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>13611800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>12624100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>11572000</v>
       </c>
     </row>
-    <row r="73" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -4582,8 +4934,14 @@
       <c r="W73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -4647,8 +5005,14 @@
       <c r="W74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -4712,73 +5076,85 @@
       <c r="W75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>17492000</v>
+      </c>
+      <c r="E76" s="3">
+        <v>17492000</v>
+      </c>
+      <c r="F76" s="3">
         <v>16171000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>16171000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>17823000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>17823000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>17159000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>17159000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>16731000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>20878000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>19110000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>19477000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>25037000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>21968000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>15882000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>16087000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>15449000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>14666000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>18881500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>16897300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>15938400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>15552600</v>
       </c>
     </row>
-    <row r="77" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -4842,143 +5218,161 @@
       <c r="W77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:23" x14ac:dyDescent="0.2">
+      <c r="X77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:25" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:23" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:25" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45565</v>
+      </c>
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45107</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45016</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>44196</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>44012</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>43830</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>43646</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>43465</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>43281</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>43100</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>42916</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>42735</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>42551</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>42369</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>42185</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>42004</v>
       </c>
     </row>
-    <row r="81" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1082500</v>
+      </c>
+      <c r="E81" s="3">
+        <v>1082500</v>
+      </c>
+      <c r="F81" s="3">
         <v>60000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>60000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>378500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>378500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>472000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>472000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>250500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>1606000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>512000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>-1204000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>2632000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>4019000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>1355000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>884000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>1505000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>1234000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>888200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>1488200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>1893500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>1410300</v>
       </c>
     </row>
-    <row r="82" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5002,38 +5396,40 @@
       <c r="U82" s="3"/>
       <c r="V82" s="3"/>
       <c r="W82" s="3"/>
-    </row>
-    <row r="83" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X82" s="3"/>
+      <c r="Y82" s="3"/>
+    </row>
+    <row r="83" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F83" s="3">
+      <c r="D83" s="3">
         <v>72500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="E83" s="3">
         <v>72500</v>
       </c>
-      <c r="H83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J83" s="3">
+      <c r="F83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H83" s="3">
+        <v>72500</v>
+      </c>
+      <c r="I83" s="3">
+        <v>72500</v>
+      </c>
+      <c r="J83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L83" s="3">
         <v>42000</v>
       </c>
-      <c r="K83" s="3">
-        <v>0</v>
-      </c>
-      <c r="L83" s="3">
-        <v>0</v>
-      </c>
       <c r="M83" s="3">
         <v>0</v>
       </c>
@@ -5067,8 +5463,14 @@
       <c r="W83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X83" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5132,8 +5534,14 @@
       <c r="W84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -5197,8 +5605,14 @@
       <c r="W85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -5262,8 +5676,14 @@
       <c r="W86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -5327,8 +5747,14 @@
       <c r="W87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -5392,73 +5818,85 @@
       <c r="W88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>718000</v>
+      </c>
+      <c r="E89" s="3">
+        <v>718000</v>
+      </c>
+      <c r="F89" s="3">
         <v>1086500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>1086500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>-217500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>-217500</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>633500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>633500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-319000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>325000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>2109000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>-5016000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-746000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>2745000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>980000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>1530000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>90000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>1398000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>1038100</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>174800</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>3159000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>1638100</v>
       </c>
     </row>
-    <row r="90" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -5482,73 +5920,81 @@
       <c r="U90" s="3"/>
       <c r="V90" s="3"/>
       <c r="W90" s="3"/>
-    </row>
-    <row r="91" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X90" s="3"/>
+      <c r="Y90" s="3"/>
+    </row>
+    <row r="91" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-37000</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-37000</v>
+      </c>
+      <c r="F91" s="3">
         <v>-13500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-13500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-13000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-13000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-9000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-9000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-10000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-14000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-43000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-43000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-16000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-100000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-59000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-78000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-56000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-316000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-41400</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-216500</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-118500</v>
       </c>
-      <c r="W91" s="3">
+      <c r="Y91" s="3">
         <v>-160600</v>
       </c>
     </row>
-    <row r="92" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -5612,8 +6058,14 @@
       <c r="W92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -5677,73 +6129,85 @@
       <c r="W93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-281000</v>
+      </c>
+      <c r="E94" s="3">
+        <v>-281000</v>
+      </c>
+      <c r="F94" s="3">
         <v>-135000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-135000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-209000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-209000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>29000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>29000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>12500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-417000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>-776000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>-236000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>-88000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-431000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-191000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>59000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>757000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-215000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-431800</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>-538700</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>-73700</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>51400</v>
       </c>
     </row>
-    <row r="95" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -5767,73 +6231,81 @@
       <c r="U95" s="3"/>
       <c r="V95" s="3"/>
       <c r="W95" s="3"/>
-    </row>
-    <row r="96" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X95" s="3"/>
+      <c r="Y95" s="3"/>
+    </row>
+    <row r="96" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>81000</v>
+      </c>
+      <c r="E96" s="3">
+        <v>81000</v>
+      </c>
+      <c r="F96" s="3">
         <v>195000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="G96" s="3">
         <v>195000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="H96" s="3">
         <v>86000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="I96" s="3">
         <v>86000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="J96" s="3">
         <v>180500</v>
       </c>
-      <c r="I96" s="3">
+      <c r="K96" s="3">
         <v>180500</v>
       </c>
-      <c r="J96" s="3">
+      <c r="L96" s="3">
         <v>77000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="M96" s="3">
         <v>-140000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="N96" s="3">
         <v>-674000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="O96" s="3">
         <v>-764000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="P96" s="3">
         <v>-870000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="Q96" s="3">
         <v>-1244000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="R96" s="3">
         <v>-840000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="S96" s="3">
         <v>-373000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="T96" s="3">
         <v>-786000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="U96" s="3">
         <v>-332000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="V96" s="3">
         <v>-1208800</v>
       </c>
-      <c r="U96" s="3">
+      <c r="W96" s="3">
         <v>-410900</v>
       </c>
-      <c r="V96" s="3">
+      <c r="X96" s="3">
         <v>-867800</v>
       </c>
-      <c r="W96" s="3">
+      <c r="Y96" s="3">
         <v>-375300</v>
       </c>
     </row>
-    <row r="97" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -5897,8 +6369,14 @@
       <c r="W97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -5962,8 +6440,14 @@
       <c r="W98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -6027,199 +6511,223 @@
       <c r="W99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:23" x14ac:dyDescent="0.2">
+      <c r="X99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-562000</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-562000</v>
+      </c>
+      <c r="F100" s="3">
         <v>-285500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-285500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-165500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-165500</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-439500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-439500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-146500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>67000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>145000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-1183000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-1274000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>214000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>-680000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>-715000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>-987000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>41000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>-532600</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>-598700</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>-283100</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>-1173300</v>
       </c>
     </row>
-    <row r="101" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>7500</v>
+      </c>
+      <c r="E101" s="3">
+        <v>7500</v>
+      </c>
+      <c r="F101" s="3">
         <v>-20000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>-20000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>2500</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>2500</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>-90000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>-90000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>-500</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>129000</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>-59000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>193000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>10000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>304000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>31000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="S101" s="3">
         <v>-77000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="T101" s="3">
         <v>-32000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="U101" s="3">
         <v>311000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="V101" s="3">
         <v>893300</v>
       </c>
-      <c r="U101" s="3">
+      <c r="W101" s="3">
         <v>289600</v>
       </c>
-      <c r="V101" s="3">
+      <c r="X101" s="3">
         <v>-314700</v>
       </c>
-      <c r="W101" s="3">
+      <c r="Y101" s="3">
         <v>150100</v>
       </c>
     </row>
-    <row r="102" spans="3:23" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:25" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-103000</v>
+      </c>
+      <c r="E102" s="3">
+        <v>-103000</v>
+      </c>
+      <c r="F102" s="3">
         <v>613500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>613500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-584500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-584500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>203000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>203000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-450500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-366000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>1419000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>-6184000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-2293000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>2547000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>140000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>797000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-172000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>1535000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>967000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>-673000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>2487400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>666300</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/PUK_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PUK_QTR_FIN.xlsx
@@ -752,10 +752,10 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>3373500</v>
+        <v>3465500</v>
       </c>
       <c r="E8" s="3">
-        <v>3373500</v>
+        <v>3465500</v>
       </c>
       <c r="F8" s="3">
         <v>2662500</v>
@@ -894,10 +894,10 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>1286000</v>
+        <v>1378000</v>
       </c>
       <c r="E10" s="3">
-        <v>1286000</v>
+        <v>1378000</v>
       </c>
       <c r="F10" s="3">
         <v>717500</v>
@@ -1134,10 +1134,10 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>1000</v>
+        <v>-34500</v>
       </c>
       <c r="E14" s="3">
-        <v>1000</v>
+        <v>-34500</v>
       </c>
       <c r="F14" s="3">
         <v>34500</v>
@@ -1205,10 +1205,10 @@
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>92000</v>
+        <v>112000</v>
       </c>
       <c r="E15" s="3">
-        <v>92000</v>
+        <v>112000</v>
       </c>
       <c r="F15" s="3">
         <v>102500</v>
@@ -1371,10 +1371,10 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>1286000</v>
+        <v>1378000</v>
       </c>
       <c r="E18" s="3">
-        <v>1286000</v>
+        <v>1378000</v>
       </c>
       <c r="F18" s="3">
         <v>717500</v>
@@ -1469,10 +1469,10 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-124500</v>
+        <v>-175500</v>
       </c>
       <c r="E20" s="3">
-        <v>-124500</v>
+        <v>-175500</v>
       </c>
       <c r="F20" s="3">
         <v>387500</v>
@@ -1540,10 +1540,10 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>1502500</v>
+        <v>1665500</v>
       </c>
       <c r="E21" s="3">
-        <v>1502500</v>
+        <v>1665500</v>
       </c>
       <c r="F21" s="3">
         <v>432500</v>
@@ -1611,10 +1611,10 @@
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>43000</v>
+        <v>221500</v>
       </c>
       <c r="E22" s="3">
-        <v>43000</v>
+        <v>221500</v>
       </c>
       <c r="F22" s="3">
         <v>42500</v>
@@ -2321,10 +2321,10 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>124500</v>
+        <v>175500</v>
       </c>
       <c r="E32" s="3">
-        <v>124500</v>
+        <v>175500</v>
       </c>
       <c r="F32" s="3">
         <v>-387500</v>
@@ -3854,10 +3854,10 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>799000</v>
+        <v>883000</v>
       </c>
       <c r="E58" s="3">
-        <v>799000</v>
+        <v>883000</v>
       </c>
       <c r="F58" s="3">
         <v>1236000</v>
@@ -3996,10 +3996,10 @@
         <v>53</v>
       </c>
       <c r="D60" s="3">
-        <v>8961000</v>
+        <v>6470000</v>
       </c>
       <c r="E60" s="3">
-        <v>8961000</v>
+        <v>6470000</v>
       </c>
       <c r="F60" s="3">
         <v>9639000</v>
@@ -4067,10 +4067,10 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>4195000</v>
+        <v>4111000</v>
       </c>
       <c r="E61" s="3">
-        <v>4195000</v>
+        <v>4111000</v>
       </c>
       <c r="F61" s="3">
         <v>4231000</v>
@@ -4138,10 +4138,10 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>148532000</v>
+        <v>151107000</v>
       </c>
       <c r="E62" s="3">
-        <v>148532000</v>
+        <v>151107000</v>
       </c>
       <c r="F62" s="3">
         <v>142242000</v>

--- a/AAII_Financials/Quarterly/PUK_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PUK_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="92">
   <si>
     <t>PUK</t>
   </si>
@@ -764,10 +764,10 @@
         <v>3205500</v>
       </c>
       <c r="F8" s="3">
-        <v>3465500</v>
+        <v>3501000</v>
       </c>
       <c r="G8" s="3">
-        <v>3465500</v>
+        <v>3501000</v>
       </c>
       <c r="H8" s="3">
         <v>2662500</v>
@@ -776,7 +776,7 @@
         <v>2662500</v>
       </c>
       <c r="J8" s="3">
-        <v>2809500</v>
+        <v>2820500</v>
       </c>
       <c r="K8" s="3">
         <v>2809500</v>
@@ -918,10 +918,10 @@
         <v>1162500</v>
       </c>
       <c r="F10" s="3">
-        <v>1378000</v>
+        <v>1413500</v>
       </c>
       <c r="G10" s="3">
-        <v>1378000</v>
+        <v>1413500</v>
       </c>
       <c r="H10" s="3">
         <v>717500</v>
@@ -930,7 +930,7 @@
         <v>717500</v>
       </c>
       <c r="J10" s="3">
-        <v>953500</v>
+        <v>964500</v>
       </c>
       <c r="K10" s="3">
         <v>953500</v>
@@ -1178,10 +1178,10 @@
         <v>8000</v>
       </c>
       <c r="F14" s="3">
-        <v>-34500</v>
+        <v>1000</v>
       </c>
       <c r="G14" s="3">
-        <v>-34500</v>
+        <v>1000</v>
       </c>
       <c r="H14" s="3">
         <v>34500</v>
@@ -1189,8 +1189,8 @@
       <c r="I14" s="3">
         <v>34500</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>8</v>
+      <c r="J14" s="3">
+        <v>11000</v>
       </c>
       <c r="K14" s="3" t="s">
         <v>8</v>
@@ -1435,10 +1435,10 @@
         <v>1162500</v>
       </c>
       <c r="F18" s="3">
-        <v>1378000</v>
+        <v>1413500</v>
       </c>
       <c r="G18" s="3">
-        <v>1378000</v>
+        <v>1413500</v>
       </c>
       <c r="H18" s="3">
         <v>717500</v>
@@ -1447,7 +1447,7 @@
         <v>717500</v>
       </c>
       <c r="J18" s="3">
-        <v>953500</v>
+        <v>964500</v>
       </c>
       <c r="K18" s="3">
         <v>953500</v>
@@ -1618,10 +1618,10 @@
         <v>1022000</v>
       </c>
       <c r="F21" s="3">
-        <v>1665500</v>
+        <v>1701000</v>
       </c>
       <c r="G21" s="3">
-        <v>1665500</v>
+        <v>1701000</v>
       </c>
       <c r="H21" s="3">
         <v>432500</v>
@@ -1630,7 +1630,7 @@
         <v>432500</v>
       </c>
       <c r="J21" s="3">
-        <v>810000</v>
+        <v>821000</v>
       </c>
       <c r="K21" s="3">
         <v>810000</v>

--- a/AAII_Financials/Quarterly/PUK_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/PUK_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="92">
   <si>
     <t>PUK</t>
   </si>
@@ -656,335 +656,359 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AA102"/>
+  <dimension ref="A5:AC102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="27" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="29" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
+        <v>45930</v>
+      </c>
+      <c r="F7" s="2">
         <v>45838</v>
       </c>
-      <c r="E7" s="2">
+      <c r="G7" s="2">
         <v>45747</v>
       </c>
-      <c r="F7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="G7" s="2">
+      <c r="I7" s="2">
         <v>45565</v>
       </c>
-      <c r="H7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="I7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="J7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="K7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="L7" s="2">
+      <c r="N7" s="2">
         <v>45107</v>
       </c>
-      <c r="M7" s="2">
+      <c r="O7" s="2">
         <v>45016</v>
       </c>
-      <c r="N7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="O7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="R7" s="2">
         <v>44012</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="S7" s="2">
         <v>43830</v>
       </c>
-      <c r="R7" s="2">
+      <c r="T7" s="2">
         <v>43646</v>
       </c>
-      <c r="S7" s="2">
+      <c r="U7" s="2">
         <v>43465</v>
       </c>
-      <c r="T7" s="2">
+      <c r="V7" s="2">
         <v>43281</v>
       </c>
-      <c r="U7" s="2">
+      <c r="W7" s="2">
         <v>43100</v>
       </c>
-      <c r="V7" s="2">
+      <c r="X7" s="2">
         <v>42916</v>
       </c>
-      <c r="W7" s="2">
+      <c r="Y7" s="2">
         <v>42735</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Z7" s="2">
         <v>42551</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="AA7" s="2">
         <v>42369</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AB7" s="2">
         <v>42185</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AC7" s="2">
         <v>42004</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>4008000</v>
+      </c>
+      <c r="E8" s="3">
+        <v>4008000</v>
+      </c>
+      <c r="F8" s="3">
         <v>3205500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="G8" s="3">
         <v>3205500</v>
       </c>
-      <c r="F8" s="3">
-        <v>3501000</v>
-      </c>
-      <c r="G8" s="3">
-        <v>3501000</v>
-      </c>
       <c r="H8" s="3">
+        <v>3373500</v>
+      </c>
+      <c r="I8" s="3">
+        <v>3373500</v>
+      </c>
+      <c r="J8" s="3">
         <v>2662500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="K8" s="3">
         <v>2662500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="L8" s="3">
         <v>2820500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="M8" s="3">
         <v>2809500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="N8" s="3">
         <v>2709500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="O8" s="3">
         <v>2709500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="P8" s="3">
         <v>2797500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="Q8" s="3">
         <v>42311000</v>
       </c>
-      <c r="P8" s="3" t="s">
+      <c r="R8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="S8" s="3">
         <v>41197000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="T8" s="3">
         <v>52539000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="U8" s="3">
         <v>35845000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="V8" s="3">
         <v>16019000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="W8" s="3">
         <v>43466000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="X8" s="3">
         <v>42924000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="Y8" s="3">
         <v>36301000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Z8" s="3">
         <v>45947800</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="AA8" s="3">
         <v>20902900</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AB8" s="3">
         <v>33287100</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AC8" s="3">
         <v>38844000</v>
       </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>2185000</v>
+      </c>
+      <c r="E9" s="3">
+        <v>2185000</v>
+      </c>
+      <c r="F9" s="3">
         <v>2043000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="G9" s="3">
         <v>2043000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="H9" s="3">
         <v>2087500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="I9" s="3">
         <v>2087500</v>
       </c>
-      <c r="H9" s="3">
+      <c r="J9" s="3">
         <v>1945000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="K9" s="3">
         <v>1945000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="L9" s="3">
         <v>1856000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="M9" s="3">
         <v>1856000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="N9" s="3">
         <v>1786000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="O9" s="3">
         <v>1786000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="P9" s="3">
         <v>1735500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="Q9" s="3">
         <v>647000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="R9" s="3">
         <v>1433000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="S9" s="3">
         <v>2068000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="T9" s="3">
         <v>2109000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="U9" s="3">
         <v>6103000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="V9" s="3">
         <v>3186000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="W9" s="3">
         <v>1792000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="X9" s="3">
         <v>1920000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="Y9" s="3">
         <v>1987000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Z9" s="3">
         <v>2197800</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="AA9" s="3">
         <v>2210800</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AB9" s="3">
         <v>2080500</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AC9" s="3">
         <v>4498200</v>
       </c>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>1823000</v>
+      </c>
+      <c r="E10" s="3">
+        <v>1823000</v>
+      </c>
+      <c r="F10" s="3">
         <v>1162500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="G10" s="3">
         <v>1162500</v>
       </c>
-      <c r="F10" s="3">
-        <v>1413500</v>
-      </c>
-      <c r="G10" s="3">
-        <v>1413500</v>
-      </c>
       <c r="H10" s="3">
+        <v>1286000</v>
+      </c>
+      <c r="I10" s="3">
+        <v>1286000</v>
+      </c>
+      <c r="J10" s="3">
         <v>717500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="K10" s="3">
         <v>717500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="L10" s="3">
         <v>964500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="M10" s="3">
         <v>953500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="N10" s="3">
         <v>923500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="O10" s="3">
         <v>923500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="P10" s="3">
         <v>1062000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="Q10" s="3">
         <v>41664000</v>
       </c>
-      <c r="P10" s="3" t="s">
+      <c r="R10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="S10" s="3">
         <v>39129000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="T10" s="3">
         <v>50430000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="U10" s="3">
         <v>29742000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="V10" s="3">
         <v>12833000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="W10" s="3">
         <v>41674000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="X10" s="3">
         <v>41004000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="Y10" s="3">
         <v>34314000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Z10" s="3">
         <v>43750000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="AA10" s="3">
         <v>18692100</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AB10" s="3">
         <v>31206600</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AC10" s="3">
         <v>34345800</v>
       </c>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1012,8 +1036,10 @@
       <c r="Y11" s="3"/>
       <c r="Z11" s="3"/>
       <c r="AA11" s="3"/>
-    </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB11" s="3"/>
+      <c r="AC11" s="3"/>
+    </row>
+    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1089,8 +1115,14 @@
       <c r="AA12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1166,37 +1198,43 @@
       <c r="AA13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB13" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="E14" s="3">
+        <v>-8000</v>
+      </c>
+      <c r="F14" s="3">
         <v>8000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="G14" s="3">
         <v>8000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="H14" s="3">
         <v>1000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="I14" s="3">
         <v>1000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="J14" s="3">
         <v>34500</v>
       </c>
-      <c r="I14" s="3">
+      <c r="K14" s="3">
         <v>34500</v>
       </c>
-      <c r="J14" s="3">
+      <c r="L14" s="3">
         <v>11000</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="M14" s="3" t="s">
         <v>8</v>
@@ -1204,100 +1242,106 @@
       <c r="N14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O14" s="3">
+      <c r="O14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q14" s="3">
         <v>30000</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
+        <v>0</v>
+      </c>
+      <c r="S14" s="3">
         <v>159000</v>
       </c>
-      <c r="R14" s="3">
+      <c r="T14" s="3">
         <v>-17000</v>
       </c>
-      <c r="S14" s="3">
+      <c r="U14" s="3">
         <v>182000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="V14" s="3">
         <v>570000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="W14" s="3">
         <v>-162000</v>
       </c>
-      <c r="V14" s="3">
+      <c r="X14" s="3">
         <v>-66000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="Y14" s="3">
         <v>238000</v>
       </c>
-      <c r="X14" s="3" t="s">
+      <c r="Z14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z14" s="3">
-        <v>0</v>
-      </c>
       <c r="AA14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="3">
         <v>2600</v>
       </c>
     </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>134500</v>
+      </c>
+      <c r="E15" s="3">
+        <v>134500</v>
+      </c>
+      <c r="F15" s="3">
         <v>117000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="G15" s="3">
         <v>117000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="H15" s="3">
         <v>112000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="I15" s="3">
         <v>112000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="J15" s="3">
         <v>102500</v>
       </c>
-      <c r="I15" s="3">
+      <c r="K15" s="3">
         <v>102500</v>
       </c>
-      <c r="J15" s="3">
+      <c r="L15" s="3">
         <v>106500</v>
       </c>
-      <c r="K15" s="3">
+      <c r="M15" s="3">
         <v>106500</v>
       </c>
-      <c r="L15" s="3">
+      <c r="N15" s="3">
         <v>108000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="O15" s="3">
         <v>108000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="P15" s="3">
         <v>169000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="Q15" s="3">
         <v>77000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="R15" s="3">
         <v>109000</v>
-      </c>
-      <c r="Q15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="R15" s="3">
-        <v>107000</v>
       </c>
       <c r="S15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T15" s="3" t="s">
-        <v>8</v>
+      <c r="T15" s="3">
+        <v>107000</v>
       </c>
       <c r="U15" s="3" t="s">
         <v>8</v>
@@ -1305,14 +1349,14 @@
       <c r="V15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W15" s="3">
-        <v>0</v>
+      <c r="W15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="X15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y15" s="3" t="s">
-        <v>8</v>
+      <c r="Y15" s="3">
+        <v>0</v>
       </c>
       <c r="Z15" s="3" t="s">
         <v>8</v>
@@ -1320,8 +1364,14 @@
       <c r="AA15" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.2">
+      <c r="AB15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC15" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1346,162 +1396,176 @@
       <c r="Y16" s="3"/>
       <c r="Z16" s="3"/>
       <c r="AA16" s="3"/>
-    </row>
-    <row r="17" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB16" s="3"/>
+      <c r="AC16" s="3"/>
+    </row>
+    <row r="17" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2185000</v>
+      </c>
+      <c r="E17" s="3">
+        <v>2185000</v>
+      </c>
+      <c r="F17" s="3">
         <v>2043000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="G17" s="3">
         <v>2043000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="H17" s="3">
         <v>2087500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="I17" s="3">
         <v>2087500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="J17" s="3">
         <v>1945000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="K17" s="3">
         <v>1945000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="L17" s="3">
         <v>1856000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="M17" s="3">
         <v>1856000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="N17" s="3">
         <v>1786000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="O17" s="3">
         <v>1786000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="P17" s="3">
         <v>1735500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="Q17" s="3">
         <v>40297000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="R17" s="3">
         <v>-6757000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="S17" s="3">
         <v>40471000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="T17" s="3">
         <v>51224000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="U17" s="3">
         <v>32167000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="V17" s="3">
         <v>14313000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="W17" s="3">
         <v>41957000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="X17" s="3">
         <v>41014000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="Y17" s="3">
         <v>34595000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Z17" s="3">
         <v>44982000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="AA17" s="3">
         <v>19189000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AB17" s="3">
         <v>30714100</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AC17" s="3">
         <v>37257300</v>
       </c>
     </row>
-    <row r="18" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>1823000</v>
+      </c>
+      <c r="E18" s="3">
+        <v>1823000</v>
+      </c>
+      <c r="F18" s="3">
         <v>1162500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="G18" s="3">
         <v>1162500</v>
       </c>
-      <c r="F18" s="3">
-        <v>1413500</v>
-      </c>
-      <c r="G18" s="3">
-        <v>1413500</v>
-      </c>
       <c r="H18" s="3">
+        <v>1286000</v>
+      </c>
+      <c r="I18" s="3">
+        <v>1286000</v>
+      </c>
+      <c r="J18" s="3">
         <v>717500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="K18" s="3">
         <v>717500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="L18" s="3">
         <v>964500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="M18" s="3">
         <v>953500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="N18" s="3">
         <v>923500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="O18" s="3">
         <v>923500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="P18" s="3">
         <v>1062000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="Q18" s="3">
         <v>2014000</v>
       </c>
-      <c r="P18" s="3" t="s">
+      <c r="R18" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="S18" s="3">
         <v>726000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="T18" s="3">
         <v>1315000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="U18" s="3">
         <v>3678000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="V18" s="3">
         <v>1706000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="W18" s="3">
         <v>1509000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="X18" s="3">
         <v>1910000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="Y18" s="3">
         <v>1706000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Z18" s="3">
         <v>965700</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="AA18" s="3">
         <v>1713900</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AB18" s="3">
         <v>2573000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AC18" s="3">
         <v>1586700</v>
       </c>
     </row>
-    <row r="19" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1529,393 +1593,425 @@
       <c r="Y19" s="3"/>
       <c r="Z19" s="3"/>
       <c r="AA19" s="3"/>
-    </row>
-    <row r="20" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB19" s="3"/>
+      <c r="AC19" s="3"/>
+    </row>
+    <row r="20" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>76000</v>
+      </c>
+      <c r="E20" s="3">
+        <v>76000</v>
+      </c>
+      <c r="F20" s="3">
         <v>257500</v>
       </c>
-      <c r="E20" s="3">
+      <c r="G20" s="3">
         <v>257500</v>
       </c>
-      <c r="F20" s="3">
-        <v>-175500</v>
-      </c>
-      <c r="G20" s="3">
-        <v>-175500</v>
-      </c>
       <c r="H20" s="3">
+        <v>-124500</v>
+      </c>
+      <c r="I20" s="3">
+        <v>-124500</v>
+      </c>
+      <c r="J20" s="3">
         <v>387500</v>
       </c>
-      <c r="I20" s="3">
+      <c r="K20" s="3">
         <v>387500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="L20" s="3">
         <v>250000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="M20" s="3">
         <v>250000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="N20" s="3">
         <v>259500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="O20" s="3">
         <v>259500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="P20" s="3">
         <v>480000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="Q20" s="3">
         <v>384000</v>
       </c>
-      <c r="P20" s="3" t="s">
+      <c r="R20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="S20" s="3">
         <v>260000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="T20" s="3">
         <v>137000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="U20" s="3">
         <v>319000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="V20" s="3">
         <v>82000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="W20" s="3">
         <v>182000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="X20" s="3">
         <v>120000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="Y20" s="3">
         <v>96000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Z20" s="3">
         <v>111200</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="AA20" s="3">
         <v>151300</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AB20" s="3">
         <v>100100</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AC20" s="3">
         <v>205400</v>
       </c>
     </row>
-    <row r="21" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>1881500</v>
+      </c>
+      <c r="E21" s="3">
+        <v>1881500</v>
+      </c>
+      <c r="F21" s="3">
         <v>1022000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="G21" s="3">
         <v>1022000</v>
       </c>
-      <c r="F21" s="3">
-        <v>1701000</v>
-      </c>
-      <c r="G21" s="3">
-        <v>1701000</v>
-      </c>
       <c r="H21" s="3">
+        <v>1522500</v>
+      </c>
+      <c r="I21" s="3">
+        <v>1522500</v>
+      </c>
+      <c r="J21" s="3">
         <v>432500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="K21" s="3">
         <v>432500</v>
       </c>
-      <c r="J21" s="3">
+      <c r="L21" s="3">
         <v>821000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="M21" s="3">
         <v>810000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="N21" s="3">
         <v>772000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="O21" s="3">
         <v>772000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="P21" s="3">
         <v>751000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="Q21" s="3">
         <v>2366000</v>
       </c>
-      <c r="P21" s="3" t="s">
+      <c r="R21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="S21" s="3">
         <v>999000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="T21" s="3">
         <v>1559000</v>
       </c>
-      <c r="S21" s="3" t="s">
+      <c r="U21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T21" s="3">
+      <c r="V21" s="3">
         <v>1822000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="W21" s="3">
         <v>1687000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="X21" s="3">
         <v>2090000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="Y21" s="3">
         <v>1811000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Z21" s="3">
         <v>1173900</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="AA21" s="3">
         <v>1889900</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AB21" s="3">
         <v>2745500</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AC21" s="3">
         <v>1792200</v>
       </c>
     </row>
-    <row r="22" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>48000</v>
+      </c>
+      <c r="E22" s="3">
+        <v>48000</v>
+      </c>
+      <c r="F22" s="3">
         <v>43500</v>
       </c>
-      <c r="E22" s="3">
+      <c r="G22" s="3">
         <v>43500</v>
       </c>
-      <c r="F22" s="3">
-        <v>221500</v>
-      </c>
-      <c r="G22" s="3">
-        <v>221500</v>
-      </c>
       <c r="H22" s="3">
+        <v>43000</v>
+      </c>
+      <c r="I22" s="3">
+        <v>43000</v>
+      </c>
+      <c r="J22" s="3">
         <v>42500</v>
       </c>
-      <c r="I22" s="3">
+      <c r="K22" s="3">
         <v>42500</v>
       </c>
-      <c r="J22" s="3">
+      <c r="L22" s="3">
         <v>189000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="M22" s="3">
         <v>189000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="N22" s="3">
         <v>42500</v>
       </c>
-      <c r="M22" s="3">
+      <c r="O22" s="3">
         <v>42500</v>
       </c>
-      <c r="N22" s="3">
+      <c r="P22" s="3">
         <v>180000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="Q22" s="3">
         <v>153000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="R22" s="3">
         <v>163000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="S22" s="3">
         <v>223000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="T22" s="3">
         <v>293000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="U22" s="3">
         <v>547000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="V22" s="3">
         <v>189000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="W22" s="3">
         <v>209000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="X22" s="3">
         <v>216000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="Y22" s="3">
         <v>191000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Z22" s="3">
         <v>218500</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="AA22" s="3">
         <v>213900</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AB22" s="3">
         <v>194900</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AC22" s="3">
         <v>225200</v>
       </c>
     </row>
-    <row r="23" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>1707000</v>
+      </c>
+      <c r="E23" s="3">
+        <v>1707000</v>
+      </c>
+      <c r="F23" s="3">
         <v>853500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="G23" s="3">
         <v>853500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="H23" s="3">
         <v>1366500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="I23" s="3">
         <v>1366500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="J23" s="3">
         <v>253000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="K23" s="3">
         <v>253000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="L23" s="3">
         <v>514500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="M23" s="3">
         <v>514500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="N23" s="3">
         <v>621500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="O23" s="3">
         <v>621500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="P23" s="3">
         <v>402000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="Q23" s="3">
         <v>2245000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="R23" s="3">
         <v>663000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="S23" s="3">
         <v>763000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="T23" s="3">
         <v>1159000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="U23" s="3">
         <v>3450000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="V23" s="3">
         <v>1599000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="W23" s="3">
         <v>1482000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="X23" s="3">
         <v>1814000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="Y23" s="3">
         <v>1611000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Z23" s="3">
         <v>858400</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="AA23" s="3">
         <v>1651300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AB23" s="3">
         <v>2478200</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AC23" s="3">
         <v>1567000</v>
       </c>
     </row>
-    <row r="24" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>327000</v>
+      </c>
+      <c r="E24" s="3">
+        <v>327000</v>
+      </c>
+      <c r="F24" s="3">
         <v>174000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="G24" s="3">
         <v>174000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="H24" s="3">
         <v>250000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="I24" s="3">
         <v>250000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="J24" s="3">
         <v>162000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="K24" s="3">
         <v>162000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="L24" s="3">
         <v>132000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="M24" s="3">
         <v>132000</v>
-      </c>
-      <c r="L24" s="3">
-        <v>148000</v>
-      </c>
-      <c r="M24" s="3">
-        <v>148000</v>
       </c>
       <c r="N24" s="3">
         <v>148000</v>
       </c>
       <c r="O24" s="3">
+        <v>148000</v>
+      </c>
+      <c r="P24" s="3">
+        <v>148000</v>
+      </c>
+      <c r="Q24" s="3">
         <v>311000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="R24" s="3">
         <v>129000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="S24" s="3">
         <v>-32000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="T24" s="3">
         <v>1000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="U24" s="3">
         <v>569000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="V24" s="3">
         <v>326000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="W24" s="3">
         <v>152000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="X24" s="3">
         <v>309000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="Y24" s="3">
         <v>377000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Z24" s="3">
         <v>-29700</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="AA24" s="3">
         <v>163000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AB24" s="3">
         <v>584700</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AC24" s="3">
         <v>156700</v>
       </c>
     </row>
-    <row r="25" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1991,162 +2087,180 @@
       <c r="AA25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB25" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>1380000</v>
+      </c>
+      <c r="E26" s="3">
+        <v>1380000</v>
+      </c>
+      <c r="F26" s="3">
         <v>679500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="G26" s="3">
         <v>679500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="H26" s="3">
         <v>1116500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="I26" s="3">
         <v>1116500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="J26" s="3">
         <v>91000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="K26" s="3">
         <v>91000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="L26" s="3">
         <v>382500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="M26" s="3">
         <v>382500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="N26" s="3">
         <v>473500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="O26" s="3">
         <v>473500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="P26" s="3">
         <v>254000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="Q26" s="3">
         <v>1934000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="R26" s="3">
         <v>534000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="S26" s="3">
         <v>795000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="T26" s="3">
         <v>1158000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="U26" s="3">
         <v>2881000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="V26" s="3">
         <v>1273000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="W26" s="3">
         <v>1330000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="X26" s="3">
         <v>1505000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="Y26" s="3">
         <v>1234000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Z26" s="3">
         <v>888200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="AA26" s="3">
         <v>1488200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AB26" s="3">
         <v>1893500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AC26" s="3">
         <v>1410300</v>
       </c>
     </row>
-    <row r="27" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>1347000</v>
+      </c>
+      <c r="E27" s="3">
+        <v>1347000</v>
+      </c>
+      <c r="F27" s="3">
         <v>642000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="G27" s="3">
         <v>642000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="H27" s="3">
         <v>1082500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="I27" s="3">
         <v>1082500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="J27" s="3">
         <v>60000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="K27" s="3">
         <v>60000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="L27" s="3">
         <v>378500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="M27" s="3">
         <v>378500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="N27" s="3">
         <v>472000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="O27" s="3">
         <v>472000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="P27" s="3">
         <v>250500</v>
       </c>
-      <c r="O27" s="3">
+      <c r="Q27" s="3">
         <v>1946000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="R27" s="3">
         <v>512000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="S27" s="3">
         <v>792000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="T27" s="3">
         <v>1152000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="U27" s="3">
         <v>2877000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="V27" s="3">
         <v>1272000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="W27" s="3">
         <v>1329000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="X27" s="3">
         <v>1505000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="Y27" s="3">
         <v>1234000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Z27" s="3">
         <v>888200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="AA27" s="3">
         <v>1488200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AB27" s="3">
         <v>1893500</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AC27" s="3">
         <v>1410300</v>
       </c>
     </row>
-    <row r="28" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2222,8 +2336,14 @@
       <c r="AA28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB28" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2261,31 +2381,31 @@
         <v>0</v>
       </c>
       <c r="O29" s="3">
+        <v>0</v>
+      </c>
+      <c r="P29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="3">
         <v>-340000</v>
       </c>
-      <c r="P29" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+      <c r="S29" s="3">
         <v>-1996000</v>
       </c>
-      <c r="R29" s="3">
+      <c r="T29" s="3">
         <v>1480000</v>
       </c>
-      <c r="S29" s="3">
+      <c r="U29" s="3">
         <v>1142000</v>
       </c>
-      <c r="T29" s="3">
+      <c r="V29" s="3">
         <v>83000</v>
       </c>
-      <c r="U29" s="3">
+      <c r="W29" s="3">
         <v>-445000</v>
-      </c>
-      <c r="V29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="W29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="X29" s="3" t="s">
         <v>8</v>
@@ -2299,8 +2419,14 @@
       <c r="AA29" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="30" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC29" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2376,8 +2502,14 @@
       <c r="AA30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2453,162 +2585,180 @@
       <c r="AA31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB31" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-76000</v>
+      </c>
+      <c r="E32" s="3">
+        <v>-76000</v>
+      </c>
+      <c r="F32" s="3">
         <v>-257500</v>
       </c>
-      <c r="E32" s="3">
+      <c r="G32" s="3">
         <v>-257500</v>
       </c>
-      <c r="F32" s="3">
-        <v>175500</v>
-      </c>
-      <c r="G32" s="3">
-        <v>175500</v>
-      </c>
       <c r="H32" s="3">
+        <v>124500</v>
+      </c>
+      <c r="I32" s="3">
+        <v>124500</v>
+      </c>
+      <c r="J32" s="3">
         <v>-387500</v>
       </c>
-      <c r="I32" s="3">
+      <c r="K32" s="3">
         <v>-387500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="L32" s="3">
         <v>-250000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="M32" s="3">
         <v>-250000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="N32" s="3">
         <v>-259500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="O32" s="3">
         <v>-259500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="P32" s="3">
         <v>-480000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="Q32" s="3">
         <v>-384000</v>
       </c>
-      <c r="P32" s="3" t="s">
+      <c r="R32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="S32" s="3">
         <v>-260000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="T32" s="3">
         <v>-137000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="U32" s="3">
         <v>-319000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="V32" s="3">
         <v>-82000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="W32" s="3">
         <v>-182000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="X32" s="3">
         <v>-120000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="Y32" s="3">
         <v>-96000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Z32" s="3">
         <v>-111200</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="AA32" s="3">
         <v>-151300</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AB32" s="3">
         <v>-100100</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AC32" s="3">
         <v>-205400</v>
       </c>
     </row>
-    <row r="33" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>1347000</v>
+      </c>
+      <c r="E33" s="3">
+        <v>1347000</v>
+      </c>
+      <c r="F33" s="3">
         <v>642000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="G33" s="3">
         <v>642000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="H33" s="3">
         <v>1082500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="I33" s="3">
         <v>1082500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="J33" s="3">
         <v>60000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="K33" s="3">
         <v>60000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="L33" s="3">
         <v>378500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="M33" s="3">
         <v>378500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="N33" s="3">
         <v>472000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="O33" s="3">
         <v>472000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="P33" s="3">
         <v>250500</v>
       </c>
-      <c r="O33" s="3">
+      <c r="Q33" s="3">
         <v>1606000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="R33" s="3">
         <v>512000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="S33" s="3">
         <v>-1204000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="T33" s="3">
         <v>2632000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="U33" s="3">
         <v>4019000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="V33" s="3">
         <v>1355000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="W33" s="3">
         <v>884000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="X33" s="3">
         <v>1505000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="Y33" s="3">
         <v>1234000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Z33" s="3">
         <v>888200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="AA33" s="3">
         <v>1488200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AB33" s="3">
         <v>1893500</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AC33" s="3">
         <v>1410300</v>
       </c>
     </row>
-    <row r="34" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -2684,167 +2834,185 @@
       <c r="AA34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB34" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>1347000</v>
+      </c>
+      <c r="E35" s="3">
+        <v>1347000</v>
+      </c>
+      <c r="F35" s="3">
         <v>642000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="G35" s="3">
         <v>642000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="H35" s="3">
         <v>1082500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="I35" s="3">
         <v>1082500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="J35" s="3">
         <v>60000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="K35" s="3">
         <v>60000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="L35" s="3">
         <v>378500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="M35" s="3">
         <v>378500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="N35" s="3">
         <v>472000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="O35" s="3">
         <v>472000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="P35" s="3">
         <v>250500</v>
       </c>
-      <c r="O35" s="3">
+      <c r="Q35" s="3">
         <v>1606000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="R35" s="3">
         <v>512000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="S35" s="3">
         <v>-1204000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="T35" s="3">
         <v>2632000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="U35" s="3">
         <v>4019000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="V35" s="3">
         <v>1355000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="W35" s="3">
         <v>884000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="X35" s="3">
         <v>1505000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="Y35" s="3">
         <v>1234000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Z35" s="3">
         <v>888200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="AA35" s="3">
         <v>1488200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AB35" s="3">
         <v>1893500</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AC35" s="3">
         <v>1410300</v>
       </c>
     </row>
-    <row r="37" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
+        <v>45930</v>
+      </c>
+      <c r="F38" s="2">
         <v>45838</v>
       </c>
-      <c r="E38" s="2">
+      <c r="G38" s="2">
         <v>45747</v>
       </c>
-      <c r="F38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="G38" s="2">
+      <c r="I38" s="2">
         <v>45565</v>
       </c>
-      <c r="H38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="I38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="J38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="K38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="L38" s="2">
+      <c r="N38" s="2">
         <v>45107</v>
       </c>
-      <c r="M38" s="2">
+      <c r="O38" s="2">
         <v>45016</v>
       </c>
-      <c r="N38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="O38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="R38" s="2">
         <v>44012</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="S38" s="2">
         <v>43830</v>
       </c>
-      <c r="R38" s="2">
+      <c r="T38" s="2">
         <v>43646</v>
       </c>
-      <c r="S38" s="2">
+      <c r="U38" s="2">
         <v>43465</v>
       </c>
-      <c r="T38" s="2">
+      <c r="V38" s="2">
         <v>43281</v>
       </c>
-      <c r="U38" s="2">
+      <c r="W38" s="2">
         <v>43100</v>
       </c>
-      <c r="V38" s="2">
+      <c r="X38" s="2">
         <v>42916</v>
       </c>
-      <c r="W38" s="2">
+      <c r="Y38" s="2">
         <v>42735</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Z38" s="2">
         <v>42551</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="AA38" s="2">
         <v>42369</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AB38" s="2">
         <v>42185</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AC38" s="2">
         <v>42004</v>
       </c>
     </row>
-    <row r="39" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2872,8 +3040,10 @@
       <c r="Y39" s="3"/>
       <c r="Z39" s="3"/>
       <c r="AA39" s="3"/>
-    </row>
-    <row r="40" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB39" s="3"/>
+      <c r="AC39" s="3"/>
+    </row>
+    <row r="40" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2901,85 +3071,93 @@
       <c r="Y40" s="3"/>
       <c r="Z40" s="3"/>
       <c r="AA40" s="3"/>
-    </row>
-    <row r="41" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB40" s="3"/>
+      <c r="AC40" s="3"/>
+    </row>
+    <row r="41" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>3851000</v>
+      </c>
+      <c r="E41" s="3">
+        <v>3851000</v>
+      </c>
+      <c r="F41" s="3">
         <v>5636000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="G41" s="3">
         <v>5636000</v>
       </c>
-      <c r="F41" s="3">
-        <v>5772000</v>
-      </c>
-      <c r="G41" s="3">
-        <v>5772000</v>
-      </c>
       <c r="H41" s="3">
+        <v>2445000</v>
+      </c>
+      <c r="I41" s="3">
+        <v>2445000</v>
+      </c>
+      <c r="J41" s="3">
         <v>5978000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="K41" s="3">
         <v>5978000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="L41" s="3">
         <v>4751000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="M41" s="3">
         <v>4751000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="N41" s="3">
         <v>5920000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="O41" s="3">
         <v>5920000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="P41" s="3">
         <v>5514000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="Q41" s="3">
         <v>7431000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="R41" s="3">
         <v>7785000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="S41" s="3">
         <v>6609000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="T41" s="3">
         <v>6119000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="U41" s="3">
         <v>27051000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="V41" s="3">
         <v>8312000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="W41" s="3">
         <v>20400000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="X41" s="3">
         <v>19024000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="Y41" s="3">
         <v>9843000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Z41" s="3">
         <v>11027700</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="AA41" s="3">
         <v>9676700</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AB41" s="3">
         <v>10926700</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AC41" s="3">
         <v>8439300</v>
       </c>
     </row>
-    <row r="42" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3055,85 +3233,97 @@
       <c r="AA42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB42" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2710000</v>
+      </c>
+      <c r="E43" s="3">
+        <v>2710000</v>
+      </c>
+      <c r="F43" s="3">
         <v>4081000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="G43" s="3">
         <v>4081000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="H43" s="3">
         <v>2686000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="I43" s="3">
         <v>2686000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="J43" s="3">
         <v>3596000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="K43" s="3">
         <v>3596000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="L43" s="3">
         <v>2375000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="M43" s="3">
         <v>2375000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="N43" s="3">
         <v>2220000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="O43" s="3">
         <v>2220000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="P43" s="3">
         <v>2120000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="Q43" s="3">
         <v>3171000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="R43" s="3">
         <v>2729000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="S43" s="3">
         <v>2054000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="T43" s="3">
         <v>2159000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="U43" s="3">
         <v>7990000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="V43" s="3">
         <v>3120000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="W43" s="3">
         <v>5681000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="X43" s="3">
         <v>6610000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="Y43" s="3">
         <v>2872000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Z43" s="3">
         <v>4531300</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="AA43" s="3">
         <v>2549900</v>
       </c>
-      <c r="Z43" s="3" t="s">
+      <c r="AB43" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA43" s="3" t="s">
+      <c r="AC43" s="3" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="44" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -3170,11 +3360,11 @@
       <c r="N44" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O44" s="3">
-        <v>0</v>
-      </c>
-      <c r="P44" s="3">
-        <v>0</v>
+      <c r="O44" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P44" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q44" s="3">
         <v>0</v>
@@ -3209,50 +3399,56 @@
       <c r="AA44" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="45" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB44" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC44" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>5098000</v>
+      </c>
+      <c r="E45" s="3">
+        <v>5098000</v>
+      </c>
+      <c r="F45" s="3">
         <v>6116000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="G45" s="3">
         <v>6116000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="H45" s="3">
         <v>4983000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="I45" s="3">
         <v>4983000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="J45" s="3">
         <v>4727000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="K45" s="3">
         <v>4727000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="L45" s="3">
         <v>5284000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="M45" s="3">
         <v>5284000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="N45" s="3">
         <v>3498000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="O45" s="3">
         <v>3498000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="P45" s="3">
         <v>3408000</v>
       </c>
-      <c r="O45" s="3">
-        <v>0</v>
-      </c>
-      <c r="P45" s="3">
-        <v>0</v>
-      </c>
       <c r="Q45" s="3">
         <v>0</v>
       </c>
@@ -3286,50 +3482,56 @@
       <c r="AA45" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="46" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB45" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC45" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>15514000</v>
+      </c>
+      <c r="E46" s="3">
+        <v>15514000</v>
+      </c>
+      <c r="F46" s="3">
         <v>15833000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="G46" s="3">
         <v>15833000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="H46" s="3">
         <v>13441000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="I46" s="3">
         <v>13441000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="J46" s="3">
         <v>14301000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="K46" s="3">
         <v>14301000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="L46" s="3">
         <v>12410000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="M46" s="3">
         <v>12410000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="N46" s="3">
         <v>11638000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="O46" s="3">
         <v>11638000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="P46" s="3">
         <v>11042000</v>
       </c>
-      <c r="O46" s="3">
-        <v>0</v>
-      </c>
-      <c r="P46" s="3">
-        <v>0</v>
-      </c>
       <c r="Q46" s="3">
         <v>0</v>
       </c>
@@ -3363,239 +3565,263 @@
       <c r="AA46" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="47" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB46" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC46" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>190618000</v>
+      </c>
+      <c r="E47" s="3">
+        <v>190618000</v>
+      </c>
+      <c r="F47" s="3">
         <v>177234000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="G47" s="3">
         <v>177234000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="H47" s="3">
         <v>162684000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="I47" s="3">
         <v>162684000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="J47" s="3">
         <v>154718000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="K47" s="3">
         <v>154718000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="L47" s="3">
         <v>155627000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="M47" s="3">
         <v>155627000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="N47" s="3">
         <v>148072000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="O47" s="3">
         <v>148072000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="P47" s="3">
         <v>143229000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="Q47" s="3">
         <v>400592000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="R47" s="3">
         <v>377884000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="S47" s="3">
         <v>379715000</v>
       </c>
-      <c r="R47" s="3">
+      <c r="T47" s="3">
         <v>639141000</v>
       </c>
-      <c r="S47" s="3">
+      <c r="U47" s="3">
         <v>913733000</v>
       </c>
-      <c r="T47" s="3">
+      <c r="V47" s="3">
         <v>404637000</v>
       </c>
-      <c r="U47" s="3">
+      <c r="W47" s="3">
         <v>802481000</v>
       </c>
-      <c r="V47" s="3">
+      <c r="X47" s="3">
         <v>796888000</v>
       </c>
-      <c r="W47" s="3">
+      <c r="Y47" s="3">
         <v>388381000</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Z47" s="3">
         <v>476271200</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="AA47" s="3">
         <v>424114700</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AB47" s="3">
         <v>434640800</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AC47" s="3">
         <v>427702600</v>
       </c>
     </row>
-    <row r="48" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>530000</v>
+      </c>
+      <c r="E48" s="3">
+        <v>530000</v>
+      </c>
+      <c r="F48" s="3">
         <v>537000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="G48" s="3">
         <v>537000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="H48" s="3">
         <v>417000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="I48" s="3">
         <v>417000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="J48" s="3">
         <v>390000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="K48" s="3">
         <v>390000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="L48" s="3">
         <v>374000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="M48" s="3">
         <v>374000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="N48" s="3">
         <v>396000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="O48" s="3">
         <v>396000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="P48" s="3">
         <v>437000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="Q48" s="3">
         <v>916000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="R48" s="3">
         <v>987000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="S48" s="3">
         <v>1090000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="T48" s="3">
         <v>1798000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="U48" s="3">
         <v>24624000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="V48" s="3">
         <v>18556000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="W48" s="3">
         <v>33101000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="X48" s="3">
         <v>30513000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="Y48" s="3">
         <v>15389000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Z48" s="3">
         <v>19591200</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="AA48" s="3">
         <v>19067700</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AB48" s="3">
         <v>18755000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AC48" s="3">
         <v>18095300</v>
       </c>
     </row>
-    <row r="49" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>4860000</v>
+      </c>
+      <c r="E49" s="3">
+        <v>4860000</v>
+      </c>
+      <c r="F49" s="3">
         <v>4828000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="G49" s="3">
         <v>4828000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="H49" s="3">
         <v>4672000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="I49" s="3">
         <v>4672000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="J49" s="3">
         <v>4577000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="K49" s="3">
         <v>4577000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="L49" s="3">
         <v>4882000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="M49" s="3">
         <v>4882000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="N49" s="3">
         <v>4565000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="O49" s="3">
         <v>4565000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="P49" s="3">
         <v>4774000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="Q49" s="3">
         <v>1031000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="R49" s="3">
         <v>1008000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="S49" s="3">
         <v>1036000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="T49" s="3">
         <v>723000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="U49" s="3">
         <v>4193000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="V49" s="3">
         <v>1769000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="W49" s="3">
         <v>1627000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="X49" s="3">
         <v>1615000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="Y49" s="3">
         <v>1680000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Z49" s="3">
         <v>2226200</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="AA49" s="3">
         <v>2214700</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AB49" s="3">
         <v>2166100</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AC49" s="3">
         <v>2171400</v>
       </c>
     </row>
-    <row r="50" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -3671,8 +3897,14 @@
       <c r="AA50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB50" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -3748,8 +3980,14 @@
       <c r="AA51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB51" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -3772,61 +4010,67 @@
         <v>3000</v>
       </c>
       <c r="J52" s="3">
+        <v>3000</v>
+      </c>
+      <c r="K52" s="3">
+        <v>3000</v>
+      </c>
+      <c r="L52" s="3">
         <v>39000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="M52" s="3">
         <v>39000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="N52" s="3">
         <v>45000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="O52" s="3">
         <v>45000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="P52" s="3">
         <v>37000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="Q52" s="3">
         <v>4858000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="R52" s="3">
         <v>4259000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="S52" s="3">
         <v>4075000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="T52" s="3">
         <v>284138000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="U52" s="3">
         <v>29949000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="V52" s="3">
         <v>14459000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="W52" s="3">
         <v>5330000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="X52" s="3">
         <v>8276000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="Y52" s="3">
         <v>6027000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Z52" s="3">
         <v>4914000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="AA52" s="3">
         <v>3678200</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AB52" s="3">
         <v>3713300</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AC52" s="3">
         <v>4726000</v>
       </c>
     </row>
-    <row r="53" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -3902,85 +4146,97 @@
       <c r="AA53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB53" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>212195000</v>
+      </c>
+      <c r="E54" s="3">
+        <v>212195000</v>
+      </c>
+      <c r="F54" s="3">
         <v>199119000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="G54" s="3">
         <v>199119000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="H54" s="3">
         <v>181876000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="I54" s="3">
         <v>181876000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="J54" s="3">
         <v>174687000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="K54" s="3">
         <v>174687000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="L54" s="3">
         <v>174066000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="M54" s="3">
         <v>174066000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="N54" s="3">
         <v>165458000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="O54" s="3">
         <v>165458000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="P54" s="3">
         <v>160249000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="Q54" s="3">
         <v>516097000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="R54" s="3">
         <v>463165000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="S54" s="3">
         <v>454214000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="T54" s="3">
         <v>705945000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="U54" s="3">
         <v>647810000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="V54" s="3">
         <v>501170000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="W54" s="3">
         <v>493941000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="X54" s="3">
         <v>481130000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="Y54" s="3">
         <v>470498000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Z54" s="3">
         <v>567962500</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="AA54" s="3">
         <v>504748400</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AB54" s="3">
         <v>497616300</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AC54" s="3">
         <v>486164100</v>
       </c>
     </row>
-    <row r="55" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4008,8 +4264,10 @@
       <c r="Y55" s="3"/>
       <c r="Z55" s="3"/>
       <c r="AA55" s="3"/>
-    </row>
-    <row r="56" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB55" s="3"/>
+      <c r="AC55" s="3"/>
+    </row>
+    <row r="56" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4037,50 +4295,52 @@
       <c r="Y56" s="3"/>
       <c r="Z56" s="3"/>
       <c r="AA56" s="3"/>
-    </row>
-    <row r="57" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB56" s="3"/>
+      <c r="AC56" s="3"/>
+    </row>
+    <row r="57" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>640000</v>
+      </c>
+      <c r="E57" s="3">
+        <v>640000</v>
+      </c>
+      <c r="F57" s="3">
         <v>510000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="G57" s="3">
         <v>510000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="H57" s="3">
         <v>536000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="I57" s="3">
         <v>536000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="J57" s="3">
         <v>1379000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="K57" s="3">
         <v>1379000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="L57" s="3">
         <v>1151000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="M57" s="3">
         <v>1151000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="N57" s="3">
         <v>950000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="O57" s="3">
         <v>950000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="P57" s="3">
         <v>1175000</v>
       </c>
-      <c r="O57" s="3">
-        <v>0</v>
-      </c>
-      <c r="P57" s="3">
-        <v>0</v>
-      </c>
       <c r="Q57" s="3">
         <v>0</v>
       </c>
@@ -4114,64 +4374,70 @@
       <c r="AA57" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="58" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB57" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC57" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1361000</v>
+      </c>
+      <c r="E58" s="3">
+        <v>1361000</v>
+      </c>
+      <c r="F58" s="3">
         <v>1165000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="G58" s="3">
         <v>1165000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="H58" s="3">
         <v>883000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="I58" s="3">
         <v>883000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="J58" s="3">
         <v>1236000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="K58" s="3">
         <v>1236000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="L58" s="3">
         <v>1491000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="M58" s="3">
         <v>1491000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="N58" s="3">
         <v>1146000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="O58" s="3">
         <v>1146000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="P58" s="3">
         <v>1566000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="Q58" s="3">
         <v>501000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="R58" s="3">
         <v>506000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="S58" s="3">
         <v>549000</v>
       </c>
-      <c r="R58" s="3">
+      <c r="T58" s="3">
         <v>841000</v>
       </c>
-      <c r="S58" s="3">
+      <c r="U58" s="3">
         <v>716000</v>
-      </c>
-      <c r="T58" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="U58" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="V58" s="3" t="s">
         <v>8</v>
@@ -4179,11 +4445,11 @@
       <c r="W58" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X58" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y58" s="3">
-        <v>0</v>
+      <c r="X58" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y58" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Z58" s="3">
         <v>0</v>
@@ -4191,127 +4457,139 @@
       <c r="AA58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB58" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>4118000</v>
+      </c>
+      <c r="E59" s="3">
+        <v>4118000</v>
+      </c>
+      <c r="F59" s="3">
         <v>3804000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="G59" s="3">
         <v>3804000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="H59" s="3">
         <v>4778000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="I59" s="3">
         <v>4778000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="J59" s="3">
         <v>3816000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="K59" s="3">
         <v>3816000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="L59" s="3">
         <v>3224000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="M59" s="3">
         <v>3224000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="N59" s="3">
         <v>3397000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="O59" s="3">
         <v>3397000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="P59" s="3">
         <v>5402000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="Q59" s="3">
         <v>477515000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="R59" s="3">
         <v>429139000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="S59" s="3">
         <v>419599000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="T59" s="3">
         <v>393980000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="U59" s="3">
         <v>830364000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="V59" s="3">
         <v>453226000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="W59" s="3">
         <v>816205000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="X59" s="3">
         <v>866408000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="Y59" s="3">
         <v>369166000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Z59" s="3">
         <v>507721400</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="AA59" s="3">
         <v>399974500</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AB59" s="3">
         <v>448806800</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AC59" s="3">
         <v>360479200</v>
       </c>
     </row>
-    <row r="60" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>6485000</v>
+      </c>
+      <c r="E60" s="3">
+        <v>6485000</v>
+      </c>
+      <c r="F60" s="3">
         <v>10486000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="G60" s="3">
         <v>10486000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="H60" s="3">
         <v>6470000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="I60" s="3">
         <v>6470000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="J60" s="3">
         <v>9639000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="K60" s="3">
         <v>9639000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="L60" s="3">
         <v>6145000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="M60" s="3">
         <v>6145000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="N60" s="3">
         <v>7571000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="O60" s="3">
         <v>7571000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="P60" s="3">
         <v>8402000</v>
       </c>
-      <c r="O60" s="3">
-        <v>0</v>
-      </c>
-      <c r="P60" s="3">
-        <v>0</v>
-      </c>
       <c r="Q60" s="3">
         <v>0</v>
       </c>
@@ -4345,162 +4623,180 @@
       <c r="AA60" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="61" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB60" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC60" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>4674000</v>
+      </c>
+      <c r="E61" s="3">
+        <v>4674000</v>
+      </c>
+      <c r="F61" s="3">
         <v>4826000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="G61" s="3">
         <v>4826000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="H61" s="3">
         <v>4111000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="I61" s="3">
         <v>4111000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="J61" s="3">
         <v>4231000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="K61" s="3">
         <v>4231000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="L61" s="3">
         <v>4099000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="M61" s="3">
         <v>4099000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="N61" s="3">
         <v>4222000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="O61" s="3">
         <v>4222000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="P61" s="3">
         <v>4092000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="Q61" s="3">
         <v>8576000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="R61" s="3">
         <v>8223000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="S61" s="3">
         <v>7669000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="T61" s="3">
         <v>11004000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="U61" s="3">
         <v>15334000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="V61" s="3">
         <v>11570000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="W61" s="3">
         <v>11787000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="X61" s="3">
         <v>12046000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="Y61" s="3">
         <v>10452000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Z61" s="3">
         <v>13166000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="AA61" s="3">
         <v>10829700</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AB61" s="3">
         <v>11157200</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AC61" s="3">
         <v>10086600</v>
       </c>
     </row>
-    <row r="62" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>177846000</v>
+      </c>
+      <c r="E62" s="3">
+        <v>177846000</v>
+      </c>
+      <c r="F62" s="3">
         <v>162591000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="G62" s="3">
         <v>162591000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="H62" s="3">
         <v>151107000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="I62" s="3">
         <v>151107000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="J62" s="3">
         <v>142242000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="K62" s="3">
         <v>142242000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="L62" s="3">
         <v>144589000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="M62" s="3">
         <v>144589000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="N62" s="3">
         <v>135140000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="O62" s="3">
         <v>135140000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="P62" s="3">
         <v>129718000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="Q62" s="3">
         <v>6075000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="R62" s="3">
         <v>5278000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="S62" s="3">
         <v>5237000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="T62" s="3">
         <v>277443000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="U62" s="3">
         <v>33150000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="V62" s="3">
         <v>16420000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="W62" s="3">
         <v>9392000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="X62" s="3">
         <v>11366000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="Y62" s="3">
         <v>6761000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Z62" s="3">
         <v>6938500</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="AA62" s="3">
         <v>5195100</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AB62" s="3">
         <v>5695100</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AC62" s="3">
         <v>5650300</v>
       </c>
     </row>
-    <row r="63" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -4576,8 +4872,14 @@
       <c r="AA63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB63" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -4653,8 +4955,14 @@
       <c r="AA64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB64" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -4730,85 +5038,97 @@
       <c r="AA65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB65" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>190835000</v>
+      </c>
+      <c r="E66" s="3">
+        <v>190835000</v>
+      </c>
+      <c r="F66" s="3">
         <v>179675000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="G66" s="3">
         <v>179675000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="H66" s="3">
         <v>163202000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="I66" s="3">
         <v>163202000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="J66" s="3">
         <v>157451000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="K66" s="3">
         <v>157451000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="L66" s="3">
         <v>156083000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="M66" s="3">
         <v>156083000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="N66" s="3">
         <v>148147000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="O66" s="3">
         <v>148147000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="P66" s="3">
         <v>143351000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="Q66" s="3">
         <v>495219000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="R66" s="3">
         <v>444055000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="S66" s="3">
         <v>434737000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="T66" s="3">
         <v>680908000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="U66" s="3">
         <v>625842000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="V66" s="3">
         <v>485288000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="W66" s="3">
         <v>477854000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="X66" s="3">
         <v>465681000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="Y66" s="3">
         <v>455832000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Z66" s="3">
         <v>549081000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="AA66" s="3">
         <v>487851100</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AB66" s="3">
         <v>481677800</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AC66" s="3">
         <v>470611500</v>
       </c>
     </row>
-    <row r="67" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -4836,8 +5156,10 @@
       <c r="Y67" s="3"/>
       <c r="Z67" s="3"/>
       <c r="AA67" s="3"/>
-    </row>
-    <row r="68" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB67" s="3"/>
+      <c r="AC67" s="3"/>
+    </row>
+    <row r="68" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -4913,8 +5235,14 @@
       <c r="AA68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB68" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -4990,8 +5318,14 @@
       <c r="AA69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB69" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5067,8 +5401,14 @@
       <c r="AA70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB70" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -5144,85 +5484,97 @@
       <c r="AA71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB71" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>14086000</v>
+      </c>
+      <c r="E72" s="3">
+        <v>14086000</v>
+      </c>
+      <c r="F72" s="3">
         <v>12052000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="G72" s="3">
         <v>12052000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="H72" s="3">
         <v>11906000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="I72" s="3">
         <v>11906000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="J72" s="3">
         <v>10650000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="K72" s="3">
         <v>10650000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="L72" s="3">
         <v>11928000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="M72" s="3">
         <v>11928000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="N72" s="3">
         <v>11325000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="O72" s="3">
         <v>11325000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="P72" s="3">
         <v>10653000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="Q72" s="3">
         <v>14424000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="R72" s="3">
         <v>13420000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="S72" s="3">
         <v>13575000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="T72" s="3">
         <v>22597000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="U72" s="3">
         <v>21817000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="V72" s="3">
         <v>12954000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="W72" s="3">
         <v>12326000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="X72" s="3">
         <v>11700000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="Y72" s="3">
         <v>10942000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Z72" s="3">
         <v>13160800</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="AA72" s="3">
         <v>13611800</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AB72" s="3">
         <v>12624100</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AC72" s="3">
         <v>11572000</v>
       </c>
     </row>
-    <row r="73" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -5298,8 +5650,14 @@
       <c r="AA73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB73" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -5375,8 +5733,14 @@
       <c r="AA74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB74" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -5452,85 +5816,97 @@
       <c r="AA75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB75" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>20117000</v>
+      </c>
+      <c r="E76" s="3">
+        <v>20117000</v>
+      </c>
+      <c r="F76" s="3">
         <v>18119000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="G76" s="3">
         <v>18119000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="H76" s="3">
         <v>17492000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="I76" s="3">
         <v>17492000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="J76" s="3">
         <v>16171000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="K76" s="3">
         <v>16171000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="L76" s="3">
         <v>17823000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="M76" s="3">
         <v>17823000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="N76" s="3">
         <v>17159000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="O76" s="3">
         <v>17159000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="P76" s="3">
         <v>16731000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="Q76" s="3">
         <v>20878000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="R76" s="3">
         <v>19110000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="S76" s="3">
         <v>19477000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="T76" s="3">
         <v>25037000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="U76" s="3">
         <v>21968000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="V76" s="3">
         <v>15882000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="W76" s="3">
         <v>16087000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="X76" s="3">
         <v>15449000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="Y76" s="3">
         <v>14666000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Z76" s="3">
         <v>18881500</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="AA76" s="3">
         <v>16897300</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AB76" s="3">
         <v>15938400</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AC76" s="3">
         <v>15552600</v>
       </c>
     </row>
-    <row r="77" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -5606,167 +5982,185 @@
       <c r="AA77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:27" x14ac:dyDescent="0.2">
+      <c r="AB77" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:29" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:27" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:29" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
+        <v>45930</v>
+      </c>
+      <c r="F80" s="2">
         <v>45838</v>
       </c>
-      <c r="E80" s="2">
+      <c r="G80" s="2">
         <v>45747</v>
       </c>
-      <c r="F80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="G80" s="2">
+      <c r="I80" s="2">
         <v>45565</v>
       </c>
-      <c r="H80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="I80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="J80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="K80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="L80" s="2">
+      <c r="N80" s="2">
         <v>45107</v>
       </c>
-      <c r="M80" s="2">
+      <c r="O80" s="2">
         <v>45016</v>
       </c>
-      <c r="N80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="O80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="R80" s="2">
         <v>44012</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="S80" s="2">
         <v>43830</v>
       </c>
-      <c r="R80" s="2">
+      <c r="T80" s="2">
         <v>43646</v>
       </c>
-      <c r="S80" s="2">
+      <c r="U80" s="2">
         <v>43465</v>
       </c>
-      <c r="T80" s="2">
+      <c r="V80" s="2">
         <v>43281</v>
       </c>
-      <c r="U80" s="2">
+      <c r="W80" s="2">
         <v>43100</v>
       </c>
-      <c r="V80" s="2">
+      <c r="X80" s="2">
         <v>42916</v>
       </c>
-      <c r="W80" s="2">
+      <c r="Y80" s="2">
         <v>42735</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Z80" s="2">
         <v>42551</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="AA80" s="2">
         <v>42369</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AB80" s="2">
         <v>42185</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AC80" s="2">
         <v>42004</v>
       </c>
     </row>
-    <row r="81" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>1347000</v>
+      </c>
+      <c r="E81" s="3">
+        <v>1347000</v>
+      </c>
+      <c r="F81" s="3">
         <v>642000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="G81" s="3">
         <v>642000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="H81" s="3">
         <v>1082500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="I81" s="3">
         <v>1082500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="J81" s="3">
         <v>60000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="K81" s="3">
         <v>60000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="L81" s="3">
         <v>378500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="M81" s="3">
         <v>378500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="N81" s="3">
         <v>472000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="O81" s="3">
         <v>472000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="P81" s="3">
         <v>250500</v>
       </c>
-      <c r="O81" s="3">
+      <c r="Q81" s="3">
         <v>1606000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="R81" s="3">
         <v>512000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="S81" s="3">
         <v>-1204000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="T81" s="3">
         <v>2632000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="U81" s="3">
         <v>4019000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="V81" s="3">
         <v>1355000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="W81" s="3">
         <v>884000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="X81" s="3">
         <v>1505000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="Y81" s="3">
         <v>1234000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Z81" s="3">
         <v>888200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="AA81" s="3">
         <v>1488200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AB81" s="3">
         <v>1893500</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AC81" s="3">
         <v>1410300</v>
       </c>
     </row>
-    <row r="82" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -5794,50 +6188,52 @@
       <c r="Y82" s="3"/>
       <c r="Z82" s="3"/>
       <c r="AA82" s="3"/>
-    </row>
-    <row r="83" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB82" s="3"/>
+      <c r="AC82" s="3"/>
+    </row>
+    <row r="83" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D83" s="3" t="s">
+      <c r="D83" s="3">
+        <v>67000</v>
+      </c>
+      <c r="E83" s="3">
+        <v>67000</v>
+      </c>
+      <c r="F83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E83" s="3" t="s">
+      <c r="G83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F83" s="3">
+      <c r="H83" s="3">
+        <v>154000</v>
+      </c>
+      <c r="I83" s="3">
         <v>72500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="J83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L83" s="3">
         <v>72500</v>
       </c>
-      <c r="H83" s="3" t="s">
+      <c r="M83" s="3">
+        <v>72500</v>
+      </c>
+      <c r="N83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I83" s="3" t="s">
+      <c r="O83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J83" s="3">
-        <v>72500</v>
-      </c>
-      <c r="K83" s="3">
-        <v>72500</v>
-      </c>
-      <c r="L83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N83" s="3">
+      <c r="P83" s="3">
         <v>42000</v>
       </c>
-      <c r="O83" s="3">
-        <v>0</v>
-      </c>
-      <c r="P83" s="3">
-        <v>0</v>
-      </c>
       <c r="Q83" s="3">
         <v>0</v>
       </c>
@@ -5871,8 +6267,14 @@
       <c r="AA83" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="84" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB83" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC83" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -5948,8 +6350,14 @@
       <c r="AA84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB84" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -6025,8 +6433,14 @@
       <c r="AA85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB85" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -6102,8 +6516,14 @@
       <c r="AA86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB86" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -6179,8 +6599,14 @@
       <c r="AA87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB87" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -6256,85 +6682,97 @@
       <c r="AA88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB88" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>841500</v>
+      </c>
+      <c r="E89" s="3">
+        <v>841500</v>
+      </c>
+      <c r="F89" s="3">
         <v>383500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="G89" s="3">
         <v>383500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="H89" s="3">
         <v>718000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="I89" s="3">
         <v>718000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="J89" s="3">
         <v>1086500</v>
       </c>
-      <c r="I89" s="3">
+      <c r="K89" s="3">
         <v>1086500</v>
       </c>
-      <c r="J89" s="3">
+      <c r="L89" s="3">
         <v>-217500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="M89" s="3">
         <v>-217500</v>
       </c>
-      <c r="L89" s="3">
+      <c r="N89" s="3">
         <v>633500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="O89" s="3">
         <v>633500</v>
       </c>
-      <c r="N89" s="3">
+      <c r="P89" s="3">
         <v>-319000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="Q89" s="3">
         <v>325000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="R89" s="3">
         <v>2109000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="S89" s="3">
         <v>-5016000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="T89" s="3">
         <v>-746000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="U89" s="3">
         <v>2745000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="V89" s="3">
         <v>980000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="W89" s="3">
         <v>1530000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="X89" s="3">
         <v>90000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="Y89" s="3">
         <v>1398000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Z89" s="3">
         <v>1038100</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="AA89" s="3">
         <v>174800</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AB89" s="3">
         <v>3159000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AC89" s="3">
         <v>1638100</v>
       </c>
     </row>
-    <row r="90" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -6362,85 +6800,93 @@
       <c r="Y90" s="3"/>
       <c r="Z90" s="3"/>
       <c r="AA90" s="3"/>
-    </row>
-    <row r="91" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB90" s="3"/>
+      <c r="AC90" s="3"/>
+    </row>
+    <row r="91" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-28500</v>
+      </c>
+      <c r="E91" s="3">
+        <v>-28500</v>
+      </c>
+      <c r="F91" s="3">
         <v>-23500</v>
       </c>
-      <c r="E91" s="3">
+      <c r="G91" s="3">
         <v>-23500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="H91" s="3">
         <v>-37000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="I91" s="3">
         <v>-37000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="J91" s="3">
         <v>-13500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="K91" s="3">
         <v>-13500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="L91" s="3">
         <v>-13000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="M91" s="3">
         <v>-13000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="N91" s="3">
         <v>-9000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="O91" s="3">
         <v>-9000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="P91" s="3">
         <v>-10000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="Q91" s="3">
         <v>-14000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="R91" s="3">
         <v>-43000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="S91" s="3">
         <v>-43000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="T91" s="3">
         <v>-16000</v>
       </c>
-      <c r="S91" s="3">
+      <c r="U91" s="3">
         <v>-100000</v>
       </c>
-      <c r="T91" s="3">
+      <c r="V91" s="3">
         <v>-59000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="W91" s="3">
         <v>-78000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="X91" s="3">
         <v>-56000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="Y91" s="3">
         <v>-316000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Z91" s="3">
         <v>-41400</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="AA91" s="3">
         <v>-216500</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AB91" s="3">
         <v>-118500</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AC91" s="3">
         <v>-160600</v>
       </c>
     </row>
-    <row r="92" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -6516,8 +6962,14 @@
       <c r="AA92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB92" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -6593,85 +7045,97 @@
       <c r="AA93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB93" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>691000</v>
+      </c>
+      <c r="E94" s="3">
+        <v>691000</v>
+      </c>
+      <c r="F94" s="3">
         <v>-147000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="G94" s="3">
         <v>-147000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="H94" s="3">
         <v>-281000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="I94" s="3">
         <v>-281000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="J94" s="3">
         <v>-135000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="K94" s="3">
         <v>-135000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="L94" s="3">
         <v>-209000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="M94" s="3">
         <v>-209000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="N94" s="3">
         <v>29000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="O94" s="3">
         <v>29000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="P94" s="3">
         <v>12500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="Q94" s="3">
         <v>-417000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="R94" s="3">
         <v>-776000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="S94" s="3">
         <v>-236000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="T94" s="3">
         <v>-88000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="U94" s="3">
         <v>-431000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="V94" s="3">
         <v>-191000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="W94" s="3">
         <v>59000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="X94" s="3">
         <v>757000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="Y94" s="3">
         <v>-215000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Z94" s="3">
         <v>-431800</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="AA94" s="3">
         <v>-538700</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AB94" s="3">
         <v>-73700</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AC94" s="3">
         <v>51400</v>
       </c>
     </row>
-    <row r="95" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -6699,85 +7163,93 @@
       <c r="Y95" s="3"/>
       <c r="Z95" s="3"/>
       <c r="AA95" s="3"/>
-    </row>
-    <row r="96" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB95" s="3"/>
+      <c r="AC95" s="3"/>
+    </row>
+    <row r="96" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>84000</v>
+      </c>
+      <c r="E96" s="3">
+        <v>84000</v>
+      </c>
+      <c r="F96" s="3">
         <v>213000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="G96" s="3">
         <v>213000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="H96" s="3">
         <v>81000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="I96" s="3">
         <v>81000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="J96" s="3">
         <v>195000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="K96" s="3">
         <v>195000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="L96" s="3">
         <v>86000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="M96" s="3">
         <v>86000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="N96" s="3">
         <v>180500</v>
       </c>
-      <c r="M96" s="3">
+      <c r="O96" s="3">
         <v>180500</v>
       </c>
-      <c r="N96" s="3">
+      <c r="P96" s="3">
         <v>77000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="Q96" s="3">
         <v>-140000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="R96" s="3">
         <v>-674000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="S96" s="3">
         <v>-764000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="T96" s="3">
         <v>-870000</v>
       </c>
-      <c r="S96" s="3">
+      <c r="U96" s="3">
         <v>-1244000</v>
       </c>
-      <c r="T96" s="3">
+      <c r="V96" s="3">
         <v>-840000</v>
       </c>
-      <c r="U96" s="3">
+      <c r="W96" s="3">
         <v>-373000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="X96" s="3">
         <v>-786000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="Y96" s="3">
         <v>-332000</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Z96" s="3">
         <v>-1208800</v>
       </c>
-      <c r="Y96" s="3">
+      <c r="AA96" s="3">
         <v>-410900</v>
       </c>
-      <c r="Z96" s="3">
+      <c r="AB96" s="3">
         <v>-867800</v>
       </c>
-      <c r="AA96" s="3">
+      <c r="AC96" s="3">
         <v>-375300</v>
       </c>
     </row>
-    <row r="97" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -6853,8 +7325,14 @@
       <c r="AA97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB97" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -6930,8 +7408,14 @@
       <c r="AA98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB98" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -7007,235 +7491,259 @@
       <c r="AA99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:27" x14ac:dyDescent="0.2">
+      <c r="AB99" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-468500</v>
+      </c>
+      <c r="E100" s="3">
+        <v>-468500</v>
+      </c>
+      <c r="F100" s="3">
         <v>-403500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="G100" s="3">
         <v>-403500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="H100" s="3">
         <v>-562000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="I100" s="3">
         <v>-562000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="J100" s="3">
         <v>-285500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="K100" s="3">
         <v>-285500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="L100" s="3">
         <v>-165500</v>
       </c>
-      <c r="K100" s="3">
+      <c r="M100" s="3">
         <v>-165500</v>
       </c>
-      <c r="L100" s="3">
+      <c r="N100" s="3">
         <v>-439500</v>
       </c>
-      <c r="M100" s="3">
+      <c r="O100" s="3">
         <v>-439500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="P100" s="3">
         <v>-146500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="Q100" s="3">
         <v>67000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="R100" s="3">
         <v>145000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="S100" s="3">
         <v>-1183000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="T100" s="3">
         <v>-1274000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="U100" s="3">
         <v>214000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="V100" s="3">
         <v>-680000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="W100" s="3">
         <v>-715000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="X100" s="3">
         <v>-987000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="Y100" s="3">
         <v>41000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Z100" s="3">
         <v>-532600</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="AA100" s="3">
         <v>-598700</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AB100" s="3">
         <v>-283100</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AC100" s="3">
         <v>-1173300</v>
       </c>
     </row>
-    <row r="101" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>22000</v>
+      </c>
+      <c r="E101" s="3">
+        <v>22000</v>
+      </c>
+      <c r="F101" s="3">
         <v>-52500</v>
       </c>
-      <c r="E101" s="3">
+      <c r="G101" s="3">
         <v>-52500</v>
       </c>
-      <c r="F101" s="3">
+      <c r="H101" s="3">
         <v>7500</v>
       </c>
-      <c r="G101" s="3">
+      <c r="I101" s="3">
         <v>7500</v>
       </c>
-      <c r="H101" s="3">
+      <c r="J101" s="3">
         <v>-20000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="K101" s="3">
         <v>-20000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="L101" s="3">
         <v>2500</v>
       </c>
-      <c r="K101" s="3">
+      <c r="M101" s="3">
         <v>2500</v>
       </c>
-      <c r="L101" s="3">
+      <c r="N101" s="3">
         <v>-90000</v>
       </c>
-      <c r="M101" s="3">
+      <c r="O101" s="3">
         <v>-90000</v>
       </c>
-      <c r="N101" s="3">
+      <c r="P101" s="3">
         <v>-500</v>
       </c>
-      <c r="O101" s="3">
+      <c r="Q101" s="3">
         <v>129000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="R101" s="3">
         <v>-59000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="S101" s="3">
         <v>193000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="T101" s="3">
         <v>10000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="U101" s="3">
         <v>304000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="V101" s="3">
         <v>31000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="W101" s="3">
         <v>-77000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="X101" s="3">
         <v>-32000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="Y101" s="3">
         <v>311000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Z101" s="3">
         <v>893300</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="AA101" s="3">
         <v>289600</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AB101" s="3">
         <v>-314700</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AC101" s="3">
         <v>150100</v>
       </c>
     </row>
-    <row r="102" spans="3:27" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:29" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>1035000</v>
+      </c>
+      <c r="E102" s="3">
+        <v>1035000</v>
+      </c>
+      <c r="F102" s="3">
         <v>-68000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="G102" s="3">
         <v>-68000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="H102" s="3">
         <v>-103000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="I102" s="3">
         <v>-103000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="J102" s="3">
         <v>613500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="K102" s="3">
         <v>613500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="L102" s="3">
         <v>-584500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="M102" s="3">
         <v>-584500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="N102" s="3">
         <v>203000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="O102" s="3">
         <v>203000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="P102" s="3">
         <v>-450500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="Q102" s="3">
         <v>-366000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="R102" s="3">
         <v>1419000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="S102" s="3">
         <v>-6184000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="T102" s="3">
         <v>-2293000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="U102" s="3">
         <v>2547000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="V102" s="3">
         <v>140000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="W102" s="3">
         <v>797000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="X102" s="3">
         <v>-172000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="Y102" s="3">
         <v>1535000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Z102" s="3">
         <v>967000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="AA102" s="3">
         <v>-673000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AB102" s="3">
         <v>2487400</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AC102" s="3">
         <v>666300</v>
       </c>
     </row>
